--- a/samples/자표준문서.xlsx
+++ b/samples/자표준문서.xlsx
@@ -48,7 +48,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -70,11 +70,88 @@
         <color rgb="00B0B0B0"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B0B0B0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B0B0B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B0B0B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -85,6 +162,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -450,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:P22"/>
+  <dimension ref="B1:P26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -487,14 +567,14 @@
           <t>항목</t>
         </is>
       </c>
-      <c r="E1" s="1" t="n"/>
+      <c r="E1" s="4" t="n"/>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>정량규격</t>
         </is>
       </c>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
+      <c r="G1" s="5" t="n"/>
+      <c r="H1" s="4" t="n"/>
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>SPEC
@@ -538,8 +618,8 @@
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="B2" s="1" t="n"/>
-      <c r="C2" s="1" t="n"/>
+      <c r="B2" s="6" t="n"/>
+      <c r="C2" s="6" t="n"/>
       <c r="D2" s="1" t="inlineStr">
         <is>
           <t>중분류</t>
@@ -565,14 +645,14 @@
           <t>상한치</t>
         </is>
       </c>
-      <c r="I2" s="1" t="n"/>
-      <c r="J2" s="1" t="n"/>
-      <c r="K2" s="1" t="n"/>
-      <c r="L2" s="1" t="n"/>
-      <c r="M2" s="1" t="n"/>
-      <c r="N2" s="1" t="n"/>
-      <c r="O2" s="1" t="n"/>
-      <c r="P2" s="1" t="n"/>
+      <c r="I2" s="6" t="n"/>
+      <c r="J2" s="6" t="n"/>
+      <c r="K2" s="6" t="n"/>
+      <c r="L2" s="6" t="n"/>
+      <c r="M2" s="6" t="n"/>
+      <c r="N2" s="6" t="n"/>
+      <c r="O2" s="6" t="n"/>
+      <c r="P2" s="6" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
       <c r="B3" s="2" t="n">
@@ -1235,10 +1315,125 @@
       <c r="O22" s="3" t="n"/>
       <c r="P22" s="3" t="n"/>
     </row>
+    <row r="23">
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>충전온도범위(-5~5℃)</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I23" s="3" t="n"/>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>충전전류 0.1C, 충전전압 4.55V</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="n"/>
+      <c r="L23" s="3" t="n"/>
+      <c r="M23" s="3" t="n"/>
+      <c r="N23" s="3" t="n"/>
+      <c r="O23" s="3" t="n"/>
+      <c r="P23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>충전온도범위(5~12℃)</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G24" s="2" t="n"/>
+      <c r="H24" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I24" s="3" t="n"/>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>충전전류 0.3C, 충전전압 4.55V</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="n"/>
+      <c r="L24" s="3" t="n"/>
+      <c r="M24" s="3" t="n"/>
+      <c r="N24" s="3" t="n"/>
+      <c r="O24" s="3" t="n"/>
+      <c r="P24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>충전온도범위(12~15℃)</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="G25" s="2" t="n"/>
+      <c r="H25" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="I25" s="3" t="n"/>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>충전전류 0.7C, 충전전압 4.55V</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="n"/>
+      <c r="L25" s="3" t="n"/>
+      <c r="M25" s="3" t="n"/>
+      <c r="N25" s="3" t="n"/>
+      <c r="O25" s="3" t="n"/>
+      <c r="P25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="3" t="n"/>
+      <c r="D26" s="3" t="n"/>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>충전온도범위(15~45℃)</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="G26" s="2" t="n"/>
+      <c r="H26" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="I26" s="3" t="n"/>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>충전전류 1.2C, 충전전압 4.20V</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="n"/>
+      <c r="L26" s="3" t="n"/>
+      <c r="M26" s="3" t="n"/>
+      <c r="N26" s="3" t="n"/>
+      <c r="O26" s="3" t="n"/>
+      <c r="P26" s="3" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="M1:M2"/>
-    <mergeCell ref="P1:P2"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="C1:C2"/>
@@ -1247,6 +1442,7 @@
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="L1:L2"/>
     <mergeCell ref="J1:J2"/>
+    <mergeCell ref="P1:P2"/>
     <mergeCell ref="O1:O2"/>
     <mergeCell ref="N1:N2"/>
   </mergeCells>

--- a/samples/자표준문서.xlsx
+++ b/samples/자표준문서.xlsx
@@ -530,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:P26"/>
+  <dimension ref="B1:P106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -953,7 +953,7 @@
     </row>
     <row r="11">
       <c r="B11" s="2" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     </row>
     <row r="12">
       <c r="B12" s="2" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
     </row>
     <row r="13">
       <c r="B13" s="2" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
     </row>
     <row r="14">
       <c r="B14" s="2" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
@@ -1100,9 +1100,19 @@
       <c r="P14" s="3" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="2" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
+      <c r="B15" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>기본사양</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>기본사양</t>
+        </is>
+      </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
           <t>표준환경온도</t>
@@ -1127,9 +1137,19 @@
       <c r="P15" s="3" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
+      <c r="B16" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>기본사양</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>기본사양</t>
+        </is>
+      </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
           <t>평가환경습도</t>
@@ -1154,9 +1174,19 @@
       <c r="P16" s="3" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="2" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
+      <c r="B17" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>기본사양</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>기본사양</t>
+        </is>
+      </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
           <t>충전환경온도</t>
@@ -1181,9 +1211,19 @@
       <c r="P17" s="3" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="2" t="n"/>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n"/>
+      <c r="B18" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>기본사양</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>기본사양</t>
+        </is>
+      </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
           <t>방전환경온도</t>
@@ -1208,9 +1248,19 @@
       <c r="P18" s="3" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="2" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
+      <c r="B19" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>기본사양</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>기본사양</t>
+        </is>
+      </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
           <t>평가환경온도</t>
@@ -1235,9 +1285,19 @@
       <c r="P19" s="3" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
+      <c r="B20" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>기본사양</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>기본사양</t>
+        </is>
+      </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
           <t>1개월저장온도</t>
@@ -1262,9 +1322,19 @@
       <c r="P20" s="3" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="2" t="n"/>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
+      <c r="B21" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>기본사양</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>기본사양</t>
+        </is>
+      </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
           <t>3개월저장온도</t>
@@ -1289,9 +1359,19 @@
       <c r="P21" s="3" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="2" t="n"/>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n"/>
+      <c r="B22" s="2" t="n">
+        <v>210</v>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>기본사양</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>기본사양</t>
+        </is>
+      </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
           <t>1년저장온도</t>
@@ -1317,8 +1397,16 @@
     </row>
     <row r="23">
       <c r="B23" s="2" t="n"/>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>기본사양</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>기본사양</t>
+        </is>
+      </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
           <t>충전온도범위(-5~5℃)</t>
@@ -1346,8 +1434,16 @@
     </row>
     <row r="24">
       <c r="B24" s="2" t="n"/>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="n"/>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>기본사양</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>기본사양</t>
+        </is>
+      </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
           <t>충전온도범위(5~12℃)</t>
@@ -1375,8 +1471,16 @@
     </row>
     <row r="25">
       <c r="B25" s="2" t="n"/>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>기본사양</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>기본사양</t>
+        </is>
+      </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
           <t>충전온도범위(12~15℃)</t>
@@ -1404,8 +1508,16 @@
     </row>
     <row r="26">
       <c r="B26" s="2" t="n"/>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="3" t="n"/>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>기본사양</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>기본사양</t>
+        </is>
+      </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
           <t>충전온도범위(15~45℃)</t>
@@ -1430,6 +1542,4248 @@
       <c r="N26" s="3" t="n"/>
       <c r="O26" s="3" t="n"/>
       <c r="P26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>기본사양</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>기본사양</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>두께 측정방법</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="n"/>
+      <c r="G27" s="2" t="n"/>
+      <c r="H27" s="2" t="n"/>
+      <c r="I27" s="3" t="n"/>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>평판 가압법, 하중 300gf, 유지 10초</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="n"/>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>측정 지그 MS-JIG-02 사용</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>MS-TH-001</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="n"/>
+      <c r="P27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>기본사양</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>기본사양</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Recording 조건</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="2" t="n"/>
+      <c r="H28" s="2" t="n"/>
+      <c r="I28" s="3" t="n"/>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>1초 간격, 16bit 분해능</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="n"/>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>설비 로그 보존 3년</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>MS-DAQ-004</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="n"/>
+      <c r="P28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="2" t="n">
+        <v>230</v>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>기본사양</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>기본사양</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>누액 검사</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="n"/>
+      <c r="G29" s="2" t="n"/>
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="3" t="n"/>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>60℃ 24시간 방치 후 전해액 누액 없을 것</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="n"/>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>전수 검사</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>MS-LK-002</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="n"/>
+      <c r="P29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>기본사양</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>기본사양</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>수명평가 시료선정</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="2" t="n"/>
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="3" t="n"/>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>Lot 당 5셀 무작위 추출</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="n"/>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Lot 정의는 별도 합의</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>MS-SP-001</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="n"/>
+      <c r="P30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>일반특성</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>일반특성</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>외관</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="n"/>
+      <c r="G31" s="2" t="n"/>
+      <c r="H31" s="2" t="n"/>
+      <c r="I31" s="3" t="n"/>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>찍힘·스크래치·오염 없을 것</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="n"/>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>육안 검사, 조도 500lx 이상</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>MS-AP-001</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="n"/>
+      <c r="P31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>일반특성</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>일반특성</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>만충전두께 3</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>4.45 ± 0.1</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="n"/>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>충전 직후 1시간 이내 측정</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>MS-TH-001</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="n"/>
+      <c r="P32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="2" t="n">
+        <v>270</v>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>일반특성</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>일반특성</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>출하충전두께1</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>4.3 ± 0.1</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="n"/>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>출하 SOC 30% 기준</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>MS-TH-001</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="n"/>
+      <c r="P33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>일반특성</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>일반특성</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>폭치수</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>63 ± 0.2</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="n"/>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Tab 제외</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>MS-DIM-001</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="n"/>
+      <c r="P34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="2" t="n">
+        <v>290</v>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>일반특성</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>일반특성</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>총고치수</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>90.6 ± 0.3</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="n"/>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>Strip Tape 제외</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>MS-DIM-001</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="n"/>
+      <c r="P35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>일반특성</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>일반특성</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>총고치수2 (Strip Tape까지의 총길이)</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>91.4 ± 0.4</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="n"/>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>Strip Tape 포함</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>MS-DIM-001</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="n"/>
+      <c r="P36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="B37" s="2" t="n">
+        <v>310</v>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>일반특성</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>일반특성</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>셀방총고2</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>89.8 ± 0.3</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="n"/>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>파우치 실링부 제외</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>MS-DIM-001</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="n"/>
+      <c r="P37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="B38" s="2" t="n">
+        <v>320</v>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>일반특성</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>일반특성</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Cell 좌/우 총고 편차</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="n"/>
+      <c r="G38" s="2" t="n"/>
+      <c r="H38" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>≤ 0.15</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="n"/>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>좌우 3점 평균 차</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>MS-DIM-002</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="n"/>
+      <c r="P38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="B39" s="2" t="n">
+        <v>330</v>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>일반특성</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>일반특성</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>중량</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>22 ± 0.5</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="n"/>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>포장재 제외</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>MS-WT-001</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="n"/>
+      <c r="P39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="2" t="n">
+        <v>340</v>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>일반특성</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>일반특성</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>출하충전 IR</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>30 ± 15</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="n"/>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>mΩ</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>1kHz AC 측정</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>MS-IR-001</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="n"/>
+      <c r="P40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="B41" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>일반특성</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>일반특성</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>출하충전 OCV</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>3.83 ± 0.03</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="n"/>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>출하 후 24시간 경과 기준</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>MS-OCV-001</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="n"/>
+      <c r="P41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="B42" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>일반특성</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>일반특성</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>출하충전율</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>30 ± 2</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="n"/>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>항공 운송 규정 연계</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>MS-SOC-001</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="n"/>
+      <c r="P42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="B43" s="2" t="n">
+        <v>370</v>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>일반특성</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>일반특성</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>PP stripHeight</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>3 ± 0.2</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="n"/>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>Tape 부착 후 측정</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>MS-DIM-003</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="n"/>
+      <c r="P43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="B44" s="2" t="n">
+        <v>380</v>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>일반특성</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>일반특성</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>양극 Tab 위치</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>12.7 ± 0.3</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="n"/>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>셀 좌측 기준</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>MS-DIM-004</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="n"/>
+      <c r="P44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="B45" s="2" t="n">
+        <v>390</v>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>일반특성</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>일반특성</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>음극 Tab 위치</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>25.2 ± 0.3</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="n"/>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>셀 좌측 기준</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>MS-DIM-004</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="n"/>
+      <c r="P45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="B46" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>일반특성</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>일반특성</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>바인더 접착력 1</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H46" s="2" t="n"/>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>≥ 12 (typ. 18)</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="n"/>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>gf/mm</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>90도 박리 시험</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>MS-AD-001</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="n"/>
+      <c r="P46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="B47" s="2" t="n">
+        <v>410</v>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>일반특성</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>일반특성</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>실링 강도 (상부)</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="H47" s="2" t="n"/>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>≥ 45 (typ. 55)</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="n"/>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>N/15mm</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>180도 인장</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>MS-SL-001</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="n"/>
+      <c r="P47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="B48" s="2" t="n">
+        <v>420</v>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>일반특성</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>일반특성</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>실링 강도 (하부)</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H48" s="2" t="n"/>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>≥ 40 (typ. 50)</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="n"/>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>N/15mm</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>180도 인장</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>MS-SL-001</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="n"/>
+      <c r="P48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="B49" s="2" t="n">
+        <v>430</v>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>일반특성</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>일반특성</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Sepa 결착력</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H49" s="2" t="n"/>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>≥ 8 (typ. 12)</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="n"/>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>gf/mm</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>상온 24시간 후 측정</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>MS-AD-002</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="n"/>
+      <c r="P49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="B50" s="2" t="n">
+        <v>440</v>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>환경특성</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>온습도1 후 △V(2hr)</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="n"/>
+      <c r="G50" s="2" t="n"/>
+      <c r="H50" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>≤ 0.02</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="n"/>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>60℃/90%RH 48시간</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>MS-EV-101</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="n"/>
+      <c r="P50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="B51" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>환경특성</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>온습도1 후 △V(24hr)</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="n"/>
+      <c r="G51" s="2" t="n"/>
+      <c r="H51" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>≤ 0.03</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="n"/>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>60℃/90%RH 48시간</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>MS-EV-101</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="n"/>
+      <c r="P51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="B52" s="2" t="n">
+        <v>460</v>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>환경특성</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>온습도1 후 △R</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="n"/>
+      <c r="G52" s="2" t="n"/>
+      <c r="H52" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>≤ 15</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="n"/>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>초기 IR 대비</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>MS-EV-101</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="n"/>
+      <c r="P52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="B53" s="2" t="n">
+        <v>470</v>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>환경특성</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>온습도1 후 △T(2hr두께) 3</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="n"/>
+      <c r="G53" s="2" t="n"/>
+      <c r="H53" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>≤ 5</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="n"/>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>초기 두께 대비</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>MS-EV-101</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="n"/>
+      <c r="P53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="B54" s="2" t="n">
+        <v>480</v>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>환경특성</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>온습도1 후 외관</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="n"/>
+      <c r="G54" s="2" t="n"/>
+      <c r="H54" s="2" t="n"/>
+      <c r="I54" s="3" t="n"/>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>부풀음·누액·변색 없을 것</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="n"/>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>육안 검사</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>MS-EV-101</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="n"/>
+      <c r="P54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="B55" s="2" t="n">
+        <v>490</v>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>환경특성</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>온습도1 후 용량(0.2C)</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="G55" s="2" t="n"/>
+      <c r="H55" s="2" t="n"/>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>≥ 95</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="n"/>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>초기 용량 대비</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>MS-EV-101</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="n"/>
+      <c r="P55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="B56" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>환경특성</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>온습도1 후 용량(1.0C)</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="G56" s="2" t="n"/>
+      <c r="H56" s="2" t="n"/>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>≥ 93</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="n"/>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>초기 용량 대비</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
+          <t>MS-EV-101</t>
+        </is>
+      </c>
+      <c r="O56" s="3" t="n"/>
+      <c r="P56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="B57" s="2" t="n">
+        <v>510</v>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>환경특성</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>온습도1 후 7일방치OCV</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="G57" s="2" t="n"/>
+      <c r="H57" s="2" t="n"/>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>≥ 3.75</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="n"/>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>상온 7일 방치</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
+          <t>MS-EV-101</t>
+        </is>
+      </c>
+      <c r="O57" s="3" t="n"/>
+      <c r="P57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="B58" s="2" t="n">
+        <v>520</v>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>환경특성</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>온습도1 후 한계평가</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="n"/>
+      <c r="G58" s="2" t="n"/>
+      <c r="H58" s="2" t="n"/>
+      <c r="I58" s="3" t="n"/>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>발화·폭발 없을 것</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="n"/>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>안전 항목</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
+          <t>MS-EV-901</t>
+        </is>
+      </c>
+      <c r="O58" s="3" t="n"/>
+      <c r="P58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="B59" s="2" t="n">
+        <v>530</v>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>환경특성</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>온습도 후 해체</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="n"/>
+      <c r="G59" s="2" t="n"/>
+      <c r="H59" s="2" t="n"/>
+      <c r="I59" s="3" t="n"/>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>음극 표면 리튬 석출 없을 것</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="n"/>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>해체 분석</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
+          <t>MS-EV-902</t>
+        </is>
+      </c>
+      <c r="O59" s="3" t="n"/>
+      <c r="P59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="B60" s="2" t="n">
+        <v>540</v>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>환경특성</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>열충격1 후 △V  (2hr)</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="n"/>
+      <c r="G60" s="2" t="n"/>
+      <c r="H60" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>≤ 0.025</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="n"/>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-30℃↔85℃ 50사이클</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
+          <t>MS-EV-201</t>
+        </is>
+      </c>
+      <c r="O60" s="3" t="n"/>
+      <c r="P60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="B61" s="2" t="n">
+        <v>550</v>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>환경특성</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>열충격1 후 △V  (24hr)</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="n"/>
+      <c r="G61" s="2" t="n"/>
+      <c r="H61" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>≤ 0.035</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="n"/>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-30℃↔85℃ 50사이클</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
+          <t>MS-EV-201</t>
+        </is>
+      </c>
+      <c r="O61" s="3" t="n"/>
+      <c r="P61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="B62" s="2" t="n">
+        <v>560</v>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>환경특성</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>열충격1 후 △R</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="n"/>
+      <c r="G62" s="2" t="n"/>
+      <c r="H62" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>≤ 20</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="n"/>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>초기 IR 대비</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
+          <t>MS-EV-201</t>
+        </is>
+      </c>
+      <c r="O62" s="3" t="n"/>
+      <c r="P62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="B63" s="2" t="n">
+        <v>570</v>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>환경특성</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>열충격1 후 △T  (직후두께) 3</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="n"/>
+      <c r="G63" s="2" t="n"/>
+      <c r="H63" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>≤ 8</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="n"/>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>시험 직후 측정</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
+          <t>MS-EV-201</t>
+        </is>
+      </c>
+      <c r="O63" s="3" t="n"/>
+      <c r="P63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="B64" s="2" t="n">
+        <v>580</v>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>환경특성</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>열충격1 후 △T  (2hr두께) 3</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="n"/>
+      <c r="G64" s="2" t="n"/>
+      <c r="H64" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>≤ 6</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="n"/>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>2시간 후 측정</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
+          <t>MS-EV-201</t>
+        </is>
+      </c>
+      <c r="O64" s="3" t="n"/>
+      <c r="P64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="B65" s="2" t="n">
+        <v>590</v>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>환경특성</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>열충격1 후 외관</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="n"/>
+      <c r="G65" s="2" t="n"/>
+      <c r="H65" s="2" t="n"/>
+      <c r="I65" s="3" t="n"/>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>부풀음·누액·변색 없을 것</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="n"/>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>육안 검사</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
+          <t>MS-EV-201</t>
+        </is>
+      </c>
+      <c r="O65" s="3" t="n"/>
+      <c r="P65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="B66" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>환경특성</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>열충격1 후 용량(0.2C)</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="G66" s="2" t="n"/>
+      <c r="H66" s="2" t="n"/>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>≥ 93</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="n"/>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>초기 용량 대비</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
+          <t>MS-EV-201</t>
+        </is>
+      </c>
+      <c r="O66" s="3" t="n"/>
+      <c r="P66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="B67" s="2" t="n">
+        <v>610</v>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>환경특성</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>열충격1 후 용량(1.0C)</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="G67" s="2" t="n"/>
+      <c r="H67" s="2" t="n"/>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>≥ 91</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="n"/>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>초기 용량 대비</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
+          <t>MS-EV-201</t>
+        </is>
+      </c>
+      <c r="O67" s="3" t="n"/>
+      <c r="P67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="B68" s="2" t="n">
+        <v>620</v>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>환경특성</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>열충격1 후 7일방치  OCV</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="G68" s="2" t="n"/>
+      <c r="H68" s="2" t="n"/>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>≥ 3.72</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="n"/>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>상온 7일 방치</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
+          <t>MS-EV-201</t>
+        </is>
+      </c>
+      <c r="O68" s="3" t="n"/>
+      <c r="P68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="B69" s="2" t="n">
+        <v>630</v>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>환경특성</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>열충격1 후 한계평가</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="n"/>
+      <c r="G69" s="2" t="n"/>
+      <c r="H69" s="2" t="n"/>
+      <c r="I69" s="3" t="n"/>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>발화·폭발 없을 것</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="n"/>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>안전 항목</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
+          <t>MS-EV-901</t>
+        </is>
+      </c>
+      <c r="O69" s="3" t="n"/>
+      <c r="P69" s="3" t="n"/>
+    </row>
+    <row r="70">
+      <c r="B70" s="2" t="n">
+        <v>640</v>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>환경특성</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>열충격 후 해체</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="n"/>
+      <c r="G70" s="2" t="n"/>
+      <c r="H70" s="2" t="n"/>
+      <c r="I70" s="3" t="n"/>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>음극 표면 리튬 석출 없을 것</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="n"/>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>해체 분석</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
+          <t>MS-EV-902</t>
+        </is>
+      </c>
+      <c r="O70" s="3" t="n"/>
+      <c r="P70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="B71" s="2" t="n">
+        <v>650</v>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>환경특성</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>고온동작△R (2hr)</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="n"/>
+      <c r="G71" s="2" t="n"/>
+      <c r="H71" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>≤ 18</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="n"/>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>45℃ 동작</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
+          <t>MS-EV-301</t>
+        </is>
+      </c>
+      <c r="O71" s="3" t="n"/>
+      <c r="P71" s="3" t="n"/>
+    </row>
+    <row r="72">
+      <c r="B72" s="2" t="n">
+        <v>660</v>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>환경특성</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>고온동작△V (2hr)</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="n"/>
+      <c r="G72" s="2" t="n"/>
+      <c r="H72" s="2" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>≤ 0.022</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="n"/>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>45℃ 동작</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
+          <t>MS-EV-301</t>
+        </is>
+      </c>
+      <c r="O72" s="3" t="n"/>
+      <c r="P72" s="3" t="n"/>
+    </row>
+    <row r="73">
+      <c r="B73" s="2" t="n">
+        <v>670</v>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>환경특성</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>고온동작△V (24hr)</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="n"/>
+      <c r="G73" s="2" t="n"/>
+      <c r="H73" s="2" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>≤ 0.032</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="n"/>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>45℃ 동작</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
+          <t>MS-EV-301</t>
+        </is>
+      </c>
+      <c r="O73" s="3" t="n"/>
+      <c r="P73" s="3" t="n"/>
+    </row>
+    <row r="74">
+      <c r="B74" s="2" t="n">
+        <v>680</v>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>환경특성</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>고온동작△T (2hr) 3</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="n"/>
+      <c r="G74" s="2" t="n"/>
+      <c r="H74" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>≤ 7</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="n"/>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>초기 두께 대비</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
+          <t>MS-EV-301</t>
+        </is>
+      </c>
+      <c r="O74" s="3" t="n"/>
+      <c r="P74" s="3" t="n"/>
+    </row>
+    <row r="75">
+      <c r="B75" s="2" t="n">
+        <v>690</v>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>환경특성</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>고온동작 후  용량(0.2C)</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="G75" s="2" t="n"/>
+      <c r="H75" s="2" t="n"/>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>≥ 94</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="n"/>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>초기 용량 대비</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
+          <t>MS-EV-301</t>
+        </is>
+      </c>
+      <c r="O75" s="3" t="n"/>
+      <c r="P75" s="3" t="n"/>
+    </row>
+    <row r="76">
+      <c r="B76" s="2" t="n">
+        <v>700</v>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>환경특성</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>고온동작 후 용량(1.0C)</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="G76" s="2" t="n"/>
+      <c r="H76" s="2" t="n"/>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>≥ 92</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="n"/>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>초기 용량 대비</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
+          <t>MS-EV-301</t>
+        </is>
+      </c>
+      <c r="O76" s="3" t="n"/>
+      <c r="P76" s="3" t="n"/>
+    </row>
+    <row r="77">
+      <c r="B77" s="2" t="n">
+        <v>710</v>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>환경특성</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>Dyne Pen 검사</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G77" s="2" t="n"/>
+      <c r="H77" s="2" t="n"/>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>≥ 38</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="n"/>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>dyn/cm</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>파우치 표면 젖음성</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
+          <t>MS-SF-001</t>
+        </is>
+      </c>
+      <c r="O77" s="3" t="n"/>
+      <c r="P77" s="3" t="n"/>
+    </row>
+    <row r="78">
+      <c r="B78" s="2" t="n">
+        <v>720</v>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>Mass ILT/PRT</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>OCV</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>3.83 ± 0.03</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="n"/>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>양산 전수 검사</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
+          <t>MS-PRT-001</t>
+        </is>
+      </c>
+      <c r="O78" s="3" t="n"/>
+      <c r="P78" s="3" t="n"/>
+    </row>
+    <row r="79">
+      <c r="B79" s="2" t="n">
+        <v>730</v>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>Mass ILT/PRT</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>△IR</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="n"/>
+      <c r="G79" s="2" t="n"/>
+      <c r="H79" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>≤ 3</t>
+        </is>
+      </c>
+      <c r="J79" s="3" t="n"/>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>mΩ</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>Lot 내 편차</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
+          <t>MS-PRT-001</t>
+        </is>
+      </c>
+      <c r="O79" s="3" t="n"/>
+      <c r="P79" s="3" t="n"/>
+    </row>
+    <row r="80">
+      <c r="B80" s="2" t="n">
+        <v>740</v>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>Mass ILT/PRT</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G80" s="2" t="n"/>
+      <c r="H80" s="2" t="n"/>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>≥ 100</t>
+        </is>
+      </c>
+      <c r="J80" s="3" t="n"/>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>MΩ</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>500V 절연 저항</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
+          <t>MS-PRT-002</t>
+        </is>
+      </c>
+      <c r="O80" s="3" t="n"/>
+      <c r="P80" s="3" t="n"/>
+    </row>
+    <row r="81">
+      <c r="B81" s="2" t="n">
+        <v>750</v>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>Mass ILT/PRT</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>Swelling</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="n"/>
+      <c r="G81" s="2" t="n"/>
+      <c r="H81" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>≤ 0.1</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="n"/>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="L81" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>검사 전후 두께차</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
+          <t>MS-PRT-003</t>
+        </is>
+      </c>
+      <c r="O81" s="3" t="n"/>
+      <c r="P81" s="3" t="n"/>
+    </row>
+    <row r="82">
+      <c r="B82" s="2" t="n">
+        <v>760</v>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>전기적 특성</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>표준용량</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>1150</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>1180</v>
+      </c>
+      <c r="H82" s="2" t="n"/>
+      <c r="I82" s="3" t="inlineStr">
+        <is>
+          <t>≥ 1150 (typ. 1180)</t>
+        </is>
+      </c>
+      <c r="J82" s="3" t="n"/>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>mAh</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>0.2C 방전</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
+          <t>MS-CP-001</t>
+        </is>
+      </c>
+      <c r="O82" s="3" t="n"/>
+      <c r="P82" s="3" t="n"/>
+    </row>
+    <row r="83">
+      <c r="B83" s="2" t="n">
+        <v>770</v>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>전기적 특성</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>출하용량</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>340</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>355</v>
+      </c>
+      <c r="H83" s="2" t="n"/>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>≥ 340 (typ. 355)</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="n"/>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>mAh</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>출하 SOC 30% 기준</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
+          <t>MS-CP-002</t>
+        </is>
+      </c>
+      <c r="O83" s="3" t="n"/>
+      <c r="P83" s="3" t="n"/>
+    </row>
+    <row r="84">
+      <c r="B84" s="2" t="n">
+        <v>780</v>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>전기적 특성</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>출하검사용량2</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>1140</v>
+      </c>
+      <c r="G84" s="2" t="n"/>
+      <c r="H84" s="2" t="n"/>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>≥ 1140</t>
+        </is>
+      </c>
+      <c r="J84" s="3" t="n"/>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>mAh</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>샘플 검사</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
+          <t>MS-CP-003</t>
+        </is>
+      </c>
+      <c r="O84" s="3" t="n"/>
+      <c r="P84" s="3" t="n"/>
+    </row>
+    <row r="85">
+      <c r="B85" s="2" t="n">
+        <v>790</v>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>전기적 특성</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>정격용량</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>1150</v>
+      </c>
+      <c r="G85" s="2" t="n"/>
+      <c r="H85" s="2" t="n"/>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>≥ 1150</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="n"/>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>mAh</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>기본사양 30번과 동일 항목</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
+          <t>MS-CP-001</t>
+        </is>
+      </c>
+      <c r="O85" s="3" t="n"/>
+      <c r="P85" s="3" t="n"/>
+    </row>
+    <row r="86">
+      <c r="B86" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>전기적 특성</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>GB/T용량 (1.0C충전)</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>1130</v>
+      </c>
+      <c r="G86" s="2" t="n"/>
+      <c r="H86" s="2" t="n"/>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>≥ 1130</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="n"/>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>mAh</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>GB/T 18287 준용</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
+          <t>GB/T 18287</t>
+        </is>
+      </c>
+      <c r="O86" s="3" t="n"/>
+      <c r="P86" s="3" t="n"/>
+    </row>
+    <row r="87">
+      <c r="B87" s="2" t="n">
+        <v>810</v>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>전기적 특성</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>율별방전 : 0.2C</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="G87" s="2" t="n"/>
+      <c r="H87" s="2" t="n"/>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>≥ 99</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="n"/>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L87" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>표준용량 대비</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
+          <t>MS-RT-001</t>
+        </is>
+      </c>
+      <c r="O87" s="3" t="n"/>
+      <c r="P87" s="3" t="n"/>
+    </row>
+    <row r="88">
+      <c r="B88" s="2" t="n">
+        <v>820</v>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>전기적 특성</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>율별방전 : 0.5C</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="G88" s="2" t="n"/>
+      <c r="H88" s="2" t="n"/>
+      <c r="I88" s="3" t="inlineStr">
+        <is>
+          <t>≥ 97</t>
+        </is>
+      </c>
+      <c r="J88" s="3" t="n"/>
+      <c r="K88" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L88" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>표준용량 대비</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
+          <t>MS-RT-001</t>
+        </is>
+      </c>
+      <c r="O88" s="3" t="n"/>
+      <c r="P88" s="3" t="n"/>
+    </row>
+    <row r="89">
+      <c r="B89" s="2" t="n">
+        <v>830</v>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>전기적 특성</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>율별방전 : 1.0C</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="G89" s="2" t="n"/>
+      <c r="H89" s="2" t="n"/>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t>≥ 95</t>
+        </is>
+      </c>
+      <c r="J89" s="3" t="n"/>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L89" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>표준용량 대비</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
+          <t>MS-RT-001</t>
+        </is>
+      </c>
+      <c r="O89" s="3" t="n"/>
+      <c r="P89" s="3" t="n"/>
+    </row>
+    <row r="90">
+      <c r="B90" s="2" t="n">
+        <v>840</v>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>전기적 특성</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>온도별방전(3.0V) :  -20℃</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="G90" s="2" t="n"/>
+      <c r="H90" s="2" t="n"/>
+      <c r="I90" s="3" t="inlineStr">
+        <is>
+          <t>≥ 55</t>
+        </is>
+      </c>
+      <c r="J90" s="3" t="n"/>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L90" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>종지 3.0V</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
+          <t>MS-RT-002</t>
+        </is>
+      </c>
+      <c r="O90" s="3" t="n"/>
+      <c r="P90" s="3" t="n"/>
+    </row>
+    <row r="91">
+      <c r="B91" s="2" t="n">
+        <v>850</v>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>전기적 특성</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>온도별방전(3.0V) :  -10℃</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G91" s="2" t="n"/>
+      <c r="H91" s="2" t="n"/>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>≥ 70</t>
+        </is>
+      </c>
+      <c r="J91" s="3" t="n"/>
+      <c r="K91" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L91" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>종지 3.0V</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
+          <t>MS-RT-002</t>
+        </is>
+      </c>
+      <c r="O91" s="3" t="n"/>
+      <c r="P91" s="3" t="n"/>
+    </row>
+    <row r="92">
+      <c r="B92" s="2" t="n">
+        <v>860</v>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>전기적 특성</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>온도별방전(3.0V) :  55℃</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="G92" s="2" t="n"/>
+      <c r="H92" s="2" t="n"/>
+      <c r="I92" s="3" t="inlineStr">
+        <is>
+          <t>≥ 96</t>
+        </is>
+      </c>
+      <c r="J92" s="3" t="n"/>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L92" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>종지 3.0V</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
+          <t>MS-RT-002</t>
+        </is>
+      </c>
+      <c r="O92" s="3" t="n"/>
+      <c r="P92" s="3" t="n"/>
+    </row>
+    <row r="93">
+      <c r="B93" s="2" t="n">
+        <v>870</v>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>전기적 특성</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>만충전 상온 28일 방치  (잔존용량)</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="G93" s="2" t="n"/>
+      <c r="H93" s="2" t="n"/>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>≥ 90</t>
+        </is>
+      </c>
+      <c r="J93" s="3" t="n"/>
+      <c r="K93" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L93" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>만충전 후 방치</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
+          <t>MS-ST-001</t>
+        </is>
+      </c>
+      <c r="O93" s="3" t="n"/>
+      <c r="P93" s="3" t="n"/>
+    </row>
+    <row r="94">
+      <c r="B94" s="2" t="n">
+        <v>880</v>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>전기적 특성</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>만충전 상온 28일 방치  (회복용량)</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="G94" s="2" t="n"/>
+      <c r="H94" s="2" t="n"/>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>≥ 95</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="n"/>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L94" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>재충전 후 측정</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
+          <t>MS-ST-001</t>
+        </is>
+      </c>
+      <c r="O94" s="3" t="n"/>
+      <c r="P94" s="3" t="n"/>
+    </row>
+    <row r="95">
+      <c r="B95" s="2" t="n">
+        <v>890</v>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>전기적 특성</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>출하충전 상온 12달  방치(잔존용량)</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="G95" s="2" t="n"/>
+      <c r="H95" s="2" t="n"/>
+      <c r="I95" s="3" t="inlineStr">
+        <is>
+          <t>≥ 85</t>
+        </is>
+      </c>
+      <c r="J95" s="3" t="n"/>
+      <c r="K95" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L95" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>출하 SOC 기준</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
+          <t>MS-ST-002</t>
+        </is>
+      </c>
+      <c r="O95" s="3" t="n"/>
+      <c r="P95" s="3" t="n"/>
+    </row>
+    <row r="96">
+      <c r="B96" s="2" t="n">
+        <v>900</v>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>전기적 특성</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>출하충전 고온(45℃) 60일 방치 (잔존용량)</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="G96" s="2" t="n"/>
+      <c r="H96" s="2" t="n"/>
+      <c r="I96" s="3" t="inlineStr">
+        <is>
+          <t>≥ 80</t>
+        </is>
+      </c>
+      <c r="J96" s="3" t="n"/>
+      <c r="K96" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L96" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>고온 가속</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
+          <t>MS-ST-003</t>
+        </is>
+      </c>
+      <c r="O96" s="3" t="n"/>
+      <c r="P96" s="3" t="n"/>
+    </row>
+    <row r="97">
+      <c r="B97" s="2" t="n">
+        <v>910</v>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>전기적 특성</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>출하충전상온  1달방치(회복용량)</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="G97" s="2" t="n"/>
+      <c r="H97" s="2" t="n"/>
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t>≥ 97</t>
+        </is>
+      </c>
+      <c r="J97" s="3" t="n"/>
+      <c r="K97" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L97" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>재충전 후 측정</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
+          <t>MS-ST-002</t>
+        </is>
+      </c>
+      <c r="O97" s="3" t="n"/>
+      <c r="P97" s="3" t="n"/>
+    </row>
+    <row r="98">
+      <c r="B98" s="2" t="n">
+        <v>920</v>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>전기적 특성</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>출하충전상온  2달방치(회복용량)</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="G98" s="2" t="n"/>
+      <c r="H98" s="2" t="n"/>
+      <c r="I98" s="3" t="inlineStr">
+        <is>
+          <t>≥ 96</t>
+        </is>
+      </c>
+      <c r="J98" s="3" t="n"/>
+      <c r="K98" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L98" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>재충전 후 측정</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
+          <t>MS-ST-002</t>
+        </is>
+      </c>
+      <c r="O98" s="3" t="n"/>
+      <c r="P98" s="3" t="n"/>
+    </row>
+    <row r="99">
+      <c r="B99" s="2" t="n">
+        <v>930</v>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>전기적 특성</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>출하충전상온 3달방치(회복용량)</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="G99" s="2" t="n"/>
+      <c r="H99" s="2" t="n"/>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>≥ 95</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="n"/>
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L99" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>재충전 후 측정</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
+          <t>MS-ST-002</t>
+        </is>
+      </c>
+      <c r="O99" s="3" t="n"/>
+      <c r="P99" s="3" t="n"/>
+    </row>
+    <row r="100">
+      <c r="B100" s="2" t="n">
+        <v>940</v>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>전기적 특성</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>출하충전상온  6달방치(회복용량)</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="G100" s="2" t="n"/>
+      <c r="H100" s="2" t="n"/>
+      <c r="I100" s="3" t="inlineStr">
+        <is>
+          <t>≥ 93</t>
+        </is>
+      </c>
+      <c r="J100" s="3" t="n"/>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>재충전 후 측정</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
+          <t>MS-ST-002</t>
+        </is>
+      </c>
+      <c r="O100" s="3" t="n"/>
+      <c r="P100" s="3" t="n"/>
+    </row>
+    <row r="101">
+      <c r="B101" s="2" t="n">
+        <v>950</v>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>전기적 특성</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>1개월 출충(선박심도)  방치 후 용량측정(GB/T)</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="G101" s="2" t="n"/>
+      <c r="H101" s="2" t="n"/>
+      <c r="I101" s="3" t="inlineStr">
+        <is>
+          <t>≥ 96</t>
+        </is>
+      </c>
+      <c r="J101" s="3" t="n"/>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>선박 수송 조건</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
+          <t>GB/T 18287</t>
+        </is>
+      </c>
+      <c r="O101" s="3" t="n"/>
+      <c r="P101" s="3" t="n"/>
+    </row>
+    <row r="102">
+      <c r="B102" s="2" t="n">
+        <v>960</v>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>전기적 특성</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>2개월 출충(선박심도)  방치 후 용량측정(GB/T)</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="G102" s="2" t="n"/>
+      <c r="H102" s="2" t="n"/>
+      <c r="I102" s="3" t="inlineStr">
+        <is>
+          <t>≥ 95</t>
+        </is>
+      </c>
+      <c r="J102" s="3" t="n"/>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>선박 수송 조건</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
+          <t>GB/T 18287</t>
+        </is>
+      </c>
+      <c r="O102" s="3" t="n"/>
+      <c r="P102" s="3" t="n"/>
+    </row>
+    <row r="103">
+      <c r="B103" s="2" t="n">
+        <v>970</v>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>전기적 특성</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>3개월 출충(선박심도) 방치 후 용량측정(GB/T)</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="G103" s="2" t="n"/>
+      <c r="H103" s="2" t="n"/>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>≥ 94</t>
+        </is>
+      </c>
+      <c r="J103" s="3" t="n"/>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>선박 수송 조건</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
+          <t>GB/T 18287</t>
+        </is>
+      </c>
+      <c r="O103" s="3" t="n"/>
+      <c r="P103" s="3" t="n"/>
+    </row>
+    <row r="104">
+      <c r="B104" s="2" t="n">
+        <v>980</v>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>전기적 특성</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>6개월 출충(선박심도)  방치 후 용량측정(GB/T)</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="G104" s="2" t="n"/>
+      <c r="H104" s="2" t="n"/>
+      <c r="I104" s="3" t="inlineStr">
+        <is>
+          <t>≥ 92</t>
+        </is>
+      </c>
+      <c r="J104" s="3" t="n"/>
+      <c r="K104" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L104" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>선박 수송 조건</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
+          <t>GB/T 18287</t>
+        </is>
+      </c>
+      <c r="O104" s="3" t="n"/>
+      <c r="P104" s="3" t="n"/>
+    </row>
+    <row r="105">
+      <c r="B105" s="2" t="n">
+        <v>990</v>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>전기적 특성</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>12개월 출충(선박심도) 방치 후 용량측정(GB/T)</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="G105" s="2" t="n"/>
+      <c r="H105" s="2" t="n"/>
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t>≥ 89</t>
+        </is>
+      </c>
+      <c r="J105" s="3" t="n"/>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L105" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>선박 수송 조건</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
+          <t>GB/T 18287</t>
+        </is>
+      </c>
+      <c r="O105" s="3" t="n"/>
+      <c r="P105" s="3" t="n"/>
+    </row>
+    <row r="106">
+      <c r="B106" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성특성</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>고온방치특성</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>고온연속충전 두께 3</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="n"/>
+      <c r="G106" s="2" t="n"/>
+      <c r="H106" s="2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I106" s="3" t="inlineStr">
+        <is>
+          <t>≤ 5.2</t>
+        </is>
+      </c>
+      <c r="J106" s="3" t="n"/>
+      <c r="K106" s="3" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="L106" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>60℃ 7일 연속 충전</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
+          <t>MS-EV-401</t>
+        </is>
+      </c>
+      <c r="O106" s="3" t="n"/>
+      <c r="P106" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">

--- a/samples/자표준문서.xlsx
+++ b/samples/자표준문서.xlsx
@@ -530,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:P106"/>
+  <dimension ref="A1:P102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -1196,13 +1196,25 @@
         <v>-5</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>85</v>
-      </c>
-      <c r="I17" s="3" t="n"/>
-      <c r="J17" s="3" t="n"/>
+        <v>55</v>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>25+-30</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>-5~5℃, 0.1C(4.55V)
+5~12℃, 0.3C(4.55V)
+12~15℃, 0.8C(4.55V)
+15~45℃, 1.3C(4.10V C/O), 1.1C(4.28V), 0.8C C/O, 0.8C(4.55V) 0.1C C/O
+45~55℃, 0.8C(4.33V)</t>
+        </is>
+      </c>
       <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="n"/>
       <c r="M17" s="3" t="n"/>
@@ -1396,7 +1408,9 @@
       <c r="P22" s="3" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="2" t="n"/>
+      <c r="B23" s="2" t="n">
+        <v>90</v>
+      </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
           <t>기본사양</t>
@@ -1409,31 +1423,41 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>충전온도범위(-5~5℃)</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>-5</v>
-      </c>
+          <t>두께 측정방법</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="n"/>
       <c r="G23" s="2" t="n"/>
-      <c r="H23" s="2" t="n">
-        <v>5</v>
-      </c>
+      <c r="H23" s="2" t="n"/>
       <c r="I23" s="3" t="n"/>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>충전전류 0.1C, 충전전압 4.55V</t>
+          <t>평판 가압법, 하중 300gf, 유지 10초</t>
         </is>
       </c>
       <c r="K23" s="3" t="n"/>
-      <c r="L23" s="3" t="n"/>
-      <c r="M23" s="3" t="n"/>
-      <c r="N23" s="3" t="n"/>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>측정 지그 MS-JIG-02 사용</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>MS-TH-001</t>
+        </is>
+      </c>
       <c r="O23" s="3" t="n"/>
       <c r="P23" s="3" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="2" t="n"/>
+      <c r="B24" s="2" t="n">
+        <v>220</v>
+      </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
           <t>기본사양</t>
@@ -1446,31 +1470,41 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>충전온도범위(5~12℃)</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>5</v>
-      </c>
+          <t>Recording 조건</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n"/>
       <c r="G24" s="2" t="n"/>
-      <c r="H24" s="2" t="n">
-        <v>12</v>
-      </c>
+      <c r="H24" s="2" t="n"/>
       <c r="I24" s="3" t="n"/>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>충전전류 0.3C, 충전전압 4.55V</t>
+          <t>1초 간격, 16bit 분해능</t>
         </is>
       </c>
       <c r="K24" s="3" t="n"/>
-      <c r="L24" s="3" t="n"/>
-      <c r="M24" s="3" t="n"/>
-      <c r="N24" s="3" t="n"/>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>설비 로그 보존 3년</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>MS-DAQ-004</t>
+        </is>
+      </c>
       <c r="O24" s="3" t="n"/>
       <c r="P24" s="3" t="n"/>
     </row>
     <row r="25">
-      <c r="B25" s="2" t="n"/>
+      <c r="B25" s="2" t="n">
+        <v>230</v>
+      </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
           <t>기본사양</t>
@@ -1483,31 +1517,41 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>충전온도범위(12~15℃)</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>12</v>
-      </c>
+          <t>누액 검사</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n"/>
       <c r="G25" s="2" t="n"/>
-      <c r="H25" s="2" t="n">
-        <v>15</v>
-      </c>
+      <c r="H25" s="2" t="n"/>
       <c r="I25" s="3" t="n"/>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>충전전류 0.7C, 충전전압 4.55V</t>
+          <t>60℃ 24시간 방치 후 전해액 누액 없을 것</t>
         </is>
       </c>
       <c r="K25" s="3" t="n"/>
-      <c r="L25" s="3" t="n"/>
-      <c r="M25" s="3" t="n"/>
-      <c r="N25" s="3" t="n"/>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>전수 검사</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>MS-LK-002</t>
+        </is>
+      </c>
       <c r="O25" s="3" t="n"/>
       <c r="P25" s="3" t="n"/>
     </row>
     <row r="26">
-      <c r="B26" s="2" t="n"/>
+      <c r="B26" s="2" t="n">
+        <v>240</v>
+      </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
           <t>기본사양</t>
@@ -1520,46 +1564,54 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>충전온도범위(15~45℃)</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>15</v>
-      </c>
+          <t>수명평가 시료선정</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n"/>
       <c r="G26" s="2" t="n"/>
-      <c r="H26" s="2" t="n">
-        <v>45</v>
-      </c>
+      <c r="H26" s="2" t="n"/>
       <c r="I26" s="3" t="n"/>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>충전전류 1.2C, 충전전압 4.20V</t>
+          <t>Lot 당 5셀 무작위 추출</t>
         </is>
       </c>
       <c r="K26" s="3" t="n"/>
-      <c r="L26" s="3" t="n"/>
-      <c r="M26" s="3" t="n"/>
-      <c r="N26" s="3" t="n"/>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Lot 정의는 별도 합의</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>MS-SP-001</t>
+        </is>
+      </c>
       <c r="O26" s="3" t="n"/>
       <c r="P26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="B27" s="2" t="n">
-        <v>90</v>
+        <v>250</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>기본사양</t>
+          <t>일반특성</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>기본사양</t>
+          <t>일반특성</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>두께 측정방법</t>
+          <t>외관</t>
         </is>
       </c>
       <c r="F27" s="2" t="n"/>
@@ -1568,7 +1620,7 @@
       <c r="I27" s="3" t="n"/>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>평판 가압법, 하중 300gf, 유지 10초</t>
+          <t>찍힘·스크래치·오염 없을 것</t>
         </is>
       </c>
       <c r="K27" s="3" t="n"/>
@@ -1579,12 +1631,12 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>측정 지그 MS-JIG-02 사용</t>
+          <t>육안 검사, 조도 500lx 이상</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>MS-TH-001</t>
+          <t>MS-AP-001</t>
         </is>
       </c>
       <c r="O27" s="3" t="n"/>
@@ -1592,46 +1644,56 @@
     </row>
     <row r="28">
       <c r="B28" s="2" t="n">
-        <v>220</v>
+        <v>260</v>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>기본사양</t>
+          <t>일반특성</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>기본사양</t>
+          <t>일반특성</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Recording 조건</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="n"/>
-      <c r="G28" s="2" t="n"/>
-      <c r="H28" s="2" t="n"/>
-      <c r="I28" s="3" t="n"/>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>1초 간격, 16bit 분해능</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="n"/>
+          <t>만충전두께 3</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>4.45 ± 0.1</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="n"/>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>설비 로그 보존 3년</t>
+          <t>충전 직후 1시간 이내 측정</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>MS-DAQ-004</t>
+          <t>MS-TH-001</t>
         </is>
       </c>
       <c r="O28" s="3" t="n"/>
@@ -1639,33 +1701,43 @@
     </row>
     <row r="29">
       <c r="B29" s="2" t="n">
-        <v>230</v>
+        <v>270</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>기본사양</t>
+          <t>일반특성</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>기본사양</t>
+          <t>일반특성</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>누액 검사</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="n"/>
-      <c r="G29" s="2" t="n"/>
-      <c r="H29" s="2" t="n"/>
-      <c r="I29" s="3" t="n"/>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>60℃ 24시간 방치 후 전해액 누액 없을 것</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="n"/>
+          <t>출하충전두께1</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>4.3 ± 0.1</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="n"/>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
           <t>A</t>
@@ -1673,12 +1745,12 @@
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>전수 검사</t>
+          <t>출하 SOC 30% 기준</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>MS-LK-002</t>
+          <t>MS-TH-001</t>
         </is>
       </c>
       <c r="O29" s="3" t="n"/>
@@ -1686,46 +1758,56 @@
     </row>
     <row r="30">
       <c r="B30" s="2" t="n">
-        <v>240</v>
+        <v>280</v>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>기본사양</t>
+          <t>일반특성</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>기본사양</t>
+          <t>일반특성</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>수명평가 시료선정</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="n"/>
-      <c r="G30" s="2" t="n"/>
-      <c r="H30" s="2" t="n"/>
-      <c r="I30" s="3" t="n"/>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>Lot 당 5셀 무작위 추출</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="n"/>
+          <t>폭치수</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>63 ± 0.2</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="n"/>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>Lot 정의는 별도 합의</t>
+          <t>Tab 제외</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>MS-SP-001</t>
+          <t>MS-DIM-001</t>
         </is>
       </c>
       <c r="O30" s="3" t="n"/>
@@ -1733,7 +1815,7 @@
     </row>
     <row r="31">
       <c r="B31" s="2" t="n">
-        <v>250</v>
+        <v>290</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
@@ -1747,19 +1829,29 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>외관</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="n"/>
-      <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2" t="n"/>
-      <c r="I31" s="3" t="n"/>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>찍힘·스크래치·오염 없을 것</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="n"/>
+          <t>총고치수</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>90.6 ± 0.3</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="n"/>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
           <t>B</t>
@@ -1767,12 +1859,12 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>육안 검사, 조도 500lx 이상</t>
+          <t>Strip Tape 제외</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>MS-AP-001</t>
+          <t>MS-DIM-001</t>
         </is>
       </c>
       <c r="O31" s="3" t="n"/>
@@ -1780,7 +1872,7 @@
     </row>
     <row r="32">
       <c r="B32" s="2" t="n">
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
@@ -1794,21 +1886,21 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>만충전두께 3</t>
+          <t>총고치수2 (Strip Tape까지의 총길이)</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>4.35</v>
+        <v>91</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>4.45</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>4.55</v>
+        <v>91.8</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>4.45 ± 0.1</t>
+          <t>91.4 ± 0.4</t>
         </is>
       </c>
       <c r="J32" s="3" t="n"/>
@@ -1819,17 +1911,17 @@
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>충전 직후 1시간 이내 측정</t>
+          <t>Strip Tape 포함</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>MS-TH-001</t>
+          <t>MS-DIM-001</t>
         </is>
       </c>
       <c r="O32" s="3" t="n"/>
@@ -1837,7 +1929,7 @@
     </row>
     <row r="33">
       <c r="B33" s="2" t="n">
-        <v>270</v>
+        <v>310</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
@@ -1851,21 +1943,21 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>출하충전두께1</t>
+          <t>셀방총고2</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>4.2</v>
+        <v>89.5</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>4.3</v>
+        <v>89.8</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>4.4</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>4.3 ± 0.1</t>
+          <t>89.8 ± 0.3</t>
         </is>
       </c>
       <c r="J33" s="3" t="n"/>
@@ -1876,17 +1968,17 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>출하 SOC 30% 기준</t>
+          <t>파우치 실링부 제외</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>MS-TH-001</t>
+          <t>MS-DIM-001</t>
         </is>
       </c>
       <c r="O33" s="3" t="n"/>
@@ -1894,7 +1986,7 @@
     </row>
     <row r="34">
       <c r="B34" s="2" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
@@ -1908,21 +2000,17 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>폭치수</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>63</v>
-      </c>
+          <t>Cell 좌/우 총고 편차</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="n"/>
+      <c r="G34" s="2" t="n"/>
       <c r="H34" s="2" t="n">
-        <v>63.2</v>
+        <v>0.15</v>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>63 ± 0.2</t>
+          <t>≤ 0.15</t>
         </is>
       </c>
       <c r="J34" s="3" t="n"/>
@@ -1938,12 +2026,12 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>Tab 제외</t>
+          <t>좌우 3점 평균 차</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>MS-DIM-001</t>
+          <t>MS-DIM-002</t>
         </is>
       </c>
       <c r="O34" s="3" t="n"/>
@@ -1951,7 +2039,7 @@
     </row>
     <row r="35">
       <c r="B35" s="2" t="n">
-        <v>290</v>
+        <v>330</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
@@ -1965,27 +2053,27 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>총고치수</t>
+          <t>중량</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>90.3</v>
+        <v>21.5</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>90.59999999999999</v>
+        <v>22</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>90.90000000000001</v>
+        <v>22.5</v>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>90.6 ± 0.3</t>
+          <t>22 ± 0.5</t>
         </is>
       </c>
       <c r="J35" s="3" t="n"/>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>g</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
@@ -1995,12 +2083,12 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>Strip Tape 제외</t>
+          <t>포장재 제외</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>MS-DIM-001</t>
+          <t>MS-WT-001</t>
         </is>
       </c>
       <c r="O35" s="3" t="n"/>
@@ -2008,7 +2096,7 @@
     </row>
     <row r="36">
       <c r="B36" s="2" t="n">
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
@@ -2022,42 +2110,42 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>총고치수2 (Strip Tape까지의 총길이)</t>
+          <t>출하충전 IR</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>91</v>
+        <v>15</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>91.40000000000001</v>
+        <v>30</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>91.8</v>
+        <v>45</v>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>91.4 ± 0.4</t>
+          <t>30 ± 15</t>
         </is>
       </c>
       <c r="J36" s="3" t="n"/>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>mΩ</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>Strip Tape 포함</t>
+          <t>1kHz AC 측정</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>MS-DIM-001</t>
+          <t>MS-IR-001</t>
         </is>
       </c>
       <c r="O36" s="3" t="n"/>
@@ -2065,7 +2153,7 @@
     </row>
     <row r="37">
       <c r="B37" s="2" t="n">
-        <v>310</v>
+        <v>350</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
@@ -2079,42 +2167,42 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>셀방총고2</t>
+          <t>출하충전 OCV</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>89.5</v>
+        <v>3.8</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>89.8</v>
+        <v>3.83</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>90.09999999999999</v>
+        <v>3.86</v>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>89.8 ± 0.3</t>
+          <t>3.83 ± 0.03</t>
         </is>
       </c>
       <c r="J37" s="3" t="n"/>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>V</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>파우치 실링부 제외</t>
+          <t>출하 후 24시간 경과 기준</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>MS-DIM-001</t>
+          <t>MS-OCV-001</t>
         </is>
       </c>
       <c r="O37" s="3" t="n"/>
@@ -2122,7 +2210,7 @@
     </row>
     <row r="38">
       <c r="B38" s="2" t="n">
-        <v>320</v>
+        <v>360</v>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
@@ -2136,38 +2224,42 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Cell 좌/우 총고 편차</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="n"/>
-      <c r="G38" s="2" t="n"/>
+          <t>출하충전율</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>30</v>
+      </c>
       <c r="H38" s="2" t="n">
-        <v>0.15</v>
+        <v>32</v>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>≤ 0.15</t>
+          <t>30 ± 2</t>
         </is>
       </c>
       <c r="J38" s="3" t="n"/>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>%</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>좌우 3점 평균 차</t>
+          <t>항공 운송 규정 연계</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>MS-DIM-002</t>
+          <t>MS-SOC-001</t>
         </is>
       </c>
       <c r="O38" s="3" t="n"/>
@@ -2175,7 +2267,7 @@
     </row>
     <row r="39">
       <c r="B39" s="2" t="n">
-        <v>330</v>
+        <v>370</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
@@ -2189,42 +2281,42 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>중량</t>
+          <t>PP stripHeight</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>21.5</v>
+        <v>2.8</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>22.5</v>
+        <v>3.2</v>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>22 ± 0.5</t>
+          <t>3 ± 0.2</t>
         </is>
       </c>
       <c r="J39" s="3" t="n"/>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>포장재 제외</t>
+          <t>Tape 부착 후 측정</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>MS-WT-001</t>
+          <t>MS-DIM-003</t>
         </is>
       </c>
       <c r="O39" s="3" t="n"/>
@@ -2232,7 +2324,7 @@
     </row>
     <row r="40">
       <c r="B40" s="2" t="n">
-        <v>340</v>
+        <v>380</v>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
@@ -2246,27 +2338,27 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>출하충전 IR</t>
+          <t>양극 Tab 위치</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>15</v>
+        <v>12.4</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>30</v>
+        <v>12.7</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>30 ± 15</t>
+          <t>12.7 ± 0.3</t>
         </is>
       </c>
       <c r="J40" s="3" t="n"/>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>mΩ</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -2276,12 +2368,12 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1kHz AC 측정</t>
+          <t>셀 좌측 기준</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>MS-IR-001</t>
+          <t>MS-DIM-004</t>
         </is>
       </c>
       <c r="O40" s="3" t="n"/>
@@ -2289,7 +2381,7 @@
     </row>
     <row r="41">
       <c r="B41" s="2" t="n">
-        <v>350</v>
+        <v>390</v>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
@@ -2303,27 +2395,27 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>출하충전 OCV</t>
+          <t>음극 Tab 위치</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>3.8</v>
+        <v>24.9</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>3.83</v>
+        <v>25.2</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>3.86</v>
+        <v>25.5</v>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>3.83 ± 0.03</t>
+          <t>25.2 ± 0.3</t>
         </is>
       </c>
       <c r="J41" s="3" t="n"/>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
@@ -2333,12 +2425,12 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>출하 후 24시간 경과 기준</t>
+          <t>셀 좌측 기준</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>MS-OCV-001</t>
+          <t>MS-DIM-004</t>
         </is>
       </c>
       <c r="O41" s="3" t="n"/>
@@ -2346,7 +2438,7 @@
     </row>
     <row r="42">
       <c r="B42" s="2" t="n">
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
@@ -2360,42 +2452,40 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>출하충전율</t>
+          <t>바인더 접착력 1</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H42" s="2" t="n">
-        <v>32</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="H42" s="2" t="n"/>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>30 ± 2</t>
+          <t>≥ 12 (typ. 18)</t>
         </is>
       </c>
       <c r="J42" s="3" t="n"/>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>gf/mm</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>항공 운송 규정 연계</t>
+          <t>90도 박리 시험</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>MS-SOC-001</t>
+          <t>MS-AD-001</t>
         </is>
       </c>
       <c r="O42" s="3" t="n"/>
@@ -2403,7 +2493,7 @@
     </row>
     <row r="43">
       <c r="B43" s="2" t="n">
-        <v>370</v>
+        <v>410</v>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
@@ -2417,42 +2507,40 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>PP stripHeight</t>
+          <t>실링 강도 (상부)</t>
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>2.8</v>
+        <v>45</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H43" s="2" t="n">
-        <v>3.2</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="H43" s="2" t="n"/>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>3 ± 0.2</t>
+          <t>≥ 45 (typ. 55)</t>
         </is>
       </c>
       <c r="J43" s="3" t="n"/>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>N/15mm</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>Tape 부착 후 측정</t>
+          <t>180도 인장</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>MS-DIM-003</t>
+          <t>MS-SL-001</t>
         </is>
       </c>
       <c r="O43" s="3" t="n"/>
@@ -2460,7 +2548,7 @@
     </row>
     <row r="44">
       <c r="B44" s="2" t="n">
-        <v>380</v>
+        <v>420</v>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
@@ -2474,42 +2562,40 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>양극 Tab 위치</t>
+          <t>실링 강도 (하부)</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>12.4</v>
+        <v>40</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="H44" s="2" t="n">
-        <v>13</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="H44" s="2" t="n"/>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>12.7 ± 0.3</t>
+          <t>≥ 40 (typ. 50)</t>
         </is>
       </c>
       <c r="J44" s="3" t="n"/>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>N/15mm</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>셀 좌측 기준</t>
+          <t>180도 인장</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>MS-DIM-004</t>
+          <t>MS-SL-001</t>
         </is>
       </c>
       <c r="O44" s="3" t="n"/>
@@ -2517,7 +2603,7 @@
     </row>
     <row r="45">
       <c r="B45" s="2" t="n">
-        <v>390</v>
+        <v>430</v>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
@@ -2531,27 +2617,25 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>음극 Tab 위치</t>
+          <t>Sepa 결착력</t>
         </is>
       </c>
       <c r="F45" s="2" t="n">
-        <v>24.9</v>
+        <v>8</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="H45" s="2" t="n">
-        <v>25.5</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H45" s="2" t="n"/>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>25.2 ± 0.3</t>
+          <t>≥ 8 (typ. 12)</t>
         </is>
       </c>
       <c r="J45" s="3" t="n"/>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>gf/mm</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
@@ -2561,12 +2645,12 @@
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>셀 좌측 기준</t>
+          <t>상온 24시간 후 측정</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>MS-DIM-004</t>
+          <t>MS-AD-002</t>
         </is>
       </c>
       <c r="O45" s="3" t="n"/>
@@ -2574,54 +2658,52 @@
     </row>
     <row r="46">
       <c r="B46" s="2" t="n">
-        <v>400</v>
+        <v>440</v>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>일반특성</t>
+          <t>신뢰성특성</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>일반특성</t>
+          <t>환경특성</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>바인더 접착력 1</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="H46" s="2" t="n"/>
+          <t>온습도1 후 △V(2hr)</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="n"/>
+      <c r="G46" s="2" t="n"/>
+      <c r="H46" s="2" t="n">
+        <v>0.02</v>
+      </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>≥ 12 (typ. 18)</t>
+          <t>≤ 0.02</t>
         </is>
       </c>
       <c r="J46" s="3" t="n"/>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>gf/mm</t>
+          <t>V</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>90도 박리 시험</t>
+          <t>60℃/90%RH 48시간</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>MS-AD-001</t>
+          <t>MS-EV-101</t>
         </is>
       </c>
       <c r="O46" s="3" t="n"/>
@@ -2629,39 +2711,37 @@
     </row>
     <row r="47">
       <c r="B47" s="2" t="n">
-        <v>410</v>
+        <v>450</v>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>일반특성</t>
+          <t>신뢰성특성</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>일반특성</t>
+          <t>환경특성</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>실링 강도 (상부)</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="H47" s="2" t="n"/>
+          <t>온습도1 후 △V(24hr)</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="n"/>
+      <c r="G47" s="2" t="n"/>
+      <c r="H47" s="2" t="n">
+        <v>0.03</v>
+      </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>≥ 45 (typ. 55)</t>
+          <t>≤ 0.03</t>
         </is>
       </c>
       <c r="J47" s="3" t="n"/>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>N/15mm</t>
+          <t>V</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
@@ -2671,12 +2751,12 @@
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>180도 인장</t>
+          <t>60℃/90%RH 48시간</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>MS-SL-001</t>
+          <t>MS-EV-101</t>
         </is>
       </c>
       <c r="O47" s="3" t="n"/>
@@ -2684,54 +2764,52 @@
     </row>
     <row r="48">
       <c r="B48" s="2" t="n">
-        <v>420</v>
+        <v>460</v>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>일반특성</t>
+          <t>신뢰성특성</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>일반특성</t>
+          <t>환경특성</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>실링 강도 (하부)</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="H48" s="2" t="n"/>
+          <t>온습도1 후 △R</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="n"/>
+      <c r="G48" s="2" t="n"/>
+      <c r="H48" s="2" t="n">
+        <v>15</v>
+      </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>≥ 40 (typ. 50)</t>
+          <t>≤ 15</t>
         </is>
       </c>
       <c r="J48" s="3" t="n"/>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>N/15mm</t>
+          <t>%</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>180도 인장</t>
+          <t>초기 IR 대비</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>MS-SL-001</t>
+          <t>MS-EV-101</t>
         </is>
       </c>
       <c r="O48" s="3" t="n"/>
@@ -2739,54 +2817,52 @@
     </row>
     <row r="49">
       <c r="B49" s="2" t="n">
-        <v>430</v>
+        <v>470</v>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>일반특성</t>
+          <t>신뢰성특성</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>일반특성</t>
+          <t>환경특성</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Sepa 결착력</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G49" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="H49" s="2" t="n"/>
+          <t>온습도1 후 △T(2hr두께) 3</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="n"/>
+      <c r="G49" s="2" t="n"/>
+      <c r="H49" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>≥ 8 (typ. 12)</t>
+          <t>≤ 5</t>
         </is>
       </c>
       <c r="J49" s="3" t="n"/>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>gf/mm</t>
+          <t>%</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>상온 24시간 후 측정</t>
+          <t>초기 두께 대비</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
-          <t>MS-AD-002</t>
+          <t>MS-EV-101</t>
         </is>
       </c>
       <c r="O49" s="3" t="n"/>
@@ -2794,7 +2870,7 @@
     </row>
     <row r="50">
       <c r="B50" s="2" t="n">
-        <v>440</v>
+        <v>480</v>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
@@ -2808,25 +2884,19 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>온습도1 후 △V(2hr)</t>
+          <t>온습도1 후 외관</t>
         </is>
       </c>
       <c r="F50" s="2" t="n"/>
       <c r="G50" s="2" t="n"/>
-      <c r="H50" s="2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I50" s="3" t="inlineStr">
-        <is>
-          <t>≤ 0.02</t>
-        </is>
-      </c>
-      <c r="J50" s="3" t="n"/>
-      <c r="K50" s="3" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="H50" s="2" t="n"/>
+      <c r="I50" s="3" t="n"/>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>부풀음·누액·변색 없을 것</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="n"/>
       <c r="L50" s="3" t="inlineStr">
         <is>
           <t>A</t>
@@ -2834,7 +2904,7 @@
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>60℃/90%RH 48시간</t>
+          <t>육안 검사</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
@@ -2847,7 +2917,7 @@
     </row>
     <row r="51">
       <c r="B51" s="2" t="n">
-        <v>450</v>
+        <v>490</v>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
@@ -2861,33 +2931,33 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>온습도1 후 △V(24hr)</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="n"/>
+          <t>온습도1 후 용량(0.2C)</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>95</v>
+      </c>
       <c r="G51" s="2" t="n"/>
-      <c r="H51" s="2" t="n">
-        <v>0.03</v>
-      </c>
+      <c r="H51" s="2" t="n"/>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>≤ 0.03</t>
+          <t>≥ 95</t>
         </is>
       </c>
       <c r="J51" s="3" t="n"/>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>%</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>60℃/90%RH 48시간</t>
+          <t>초기 용량 대비</t>
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr">
@@ -2900,7 +2970,7 @@
     </row>
     <row r="52">
       <c r="B52" s="2" t="n">
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
@@ -2914,17 +2984,17 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>온습도1 후 △R</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="n"/>
+          <t>온습도1 후 용량(1.0C)</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>93</v>
+      </c>
       <c r="G52" s="2" t="n"/>
-      <c r="H52" s="2" t="n">
-        <v>15</v>
-      </c>
+      <c r="H52" s="2" t="n"/>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>≤ 15</t>
+          <t>≥ 93</t>
         </is>
       </c>
       <c r="J52" s="3" t="n"/>
@@ -2940,7 +3010,7 @@
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>초기 IR 대비</t>
+          <t>초기 용량 대비</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
@@ -2953,7 +3023,7 @@
     </row>
     <row r="53">
       <c r="B53" s="2" t="n">
-        <v>470</v>
+        <v>510</v>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
@@ -2967,23 +3037,23 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>온습도1 후 △T(2hr두께) 3</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="n"/>
+          <t>온습도1 후 7일방치OCV</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>3.75</v>
+      </c>
       <c r="G53" s="2" t="n"/>
-      <c r="H53" s="2" t="n">
-        <v>5</v>
-      </c>
+      <c r="H53" s="2" t="n"/>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>≤ 5</t>
+          <t>≥ 3.75</t>
         </is>
       </c>
       <c r="J53" s="3" t="n"/>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>V</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
@@ -2993,7 +3063,7 @@
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>초기 두께 대비</t>
+          <t>상온 7일 방치</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
@@ -3006,7 +3076,7 @@
     </row>
     <row r="54">
       <c r="B54" s="2" t="n">
-        <v>480</v>
+        <v>520</v>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
@@ -3020,7 +3090,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>온습도1 후 외관</t>
+          <t>온습도1 후 한계평가</t>
         </is>
       </c>
       <c r="F54" s="2" t="n"/>
@@ -3029,7 +3099,7 @@
       <c r="I54" s="3" t="n"/>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>부풀음·누액·변색 없을 것</t>
+          <t>발화·폭발 없을 것</t>
         </is>
       </c>
       <c r="K54" s="3" t="n"/>
@@ -3040,12 +3110,12 @@
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>육안 검사</t>
+          <t>안전 항목</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>MS-EV-101</t>
+          <t>MS-EV-901</t>
         </is>
       </c>
       <c r="O54" s="3" t="n"/>
@@ -3053,7 +3123,7 @@
     </row>
     <row r="55">
       <c r="B55" s="2" t="n">
-        <v>490</v>
+        <v>530</v>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
@@ -3067,38 +3137,32 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>온습도1 후 용량(0.2C)</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="n">
-        <v>95</v>
-      </c>
+          <t>온습도 후 해체</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="n"/>
       <c r="G55" s="2" t="n"/>
       <c r="H55" s="2" t="n"/>
-      <c r="I55" s="3" t="inlineStr">
-        <is>
-          <t>≥ 95</t>
-        </is>
-      </c>
-      <c r="J55" s="3" t="n"/>
-      <c r="K55" s="3" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
+      <c r="I55" s="3" t="n"/>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>음극 표면 리튬 석출 없을 것</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="n"/>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>초기 용량 대비</t>
+          <t>해체 분석</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>MS-EV-101</t>
+          <t>MS-EV-902</t>
         </is>
       </c>
       <c r="O55" s="3" t="n"/>
@@ -3106,7 +3170,7 @@
     </row>
     <row r="56">
       <c r="B56" s="2" t="n">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
@@ -3120,38 +3184,38 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>온습도1 후 용량(1.0C)</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="n">
-        <v>93</v>
-      </c>
+          <t>열충격1 후 △V  (2hr)</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="n"/>
       <c r="G56" s="2" t="n"/>
-      <c r="H56" s="2" t="n"/>
+      <c r="H56" s="2" t="n">
+        <v>0.025</v>
+      </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>≥ 93</t>
+          <t>≤ 0.025</t>
         </is>
       </c>
       <c r="J56" s="3" t="n"/>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>V</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>초기 용량 대비</t>
+          <t>-30℃↔85℃ 50사이클</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>MS-EV-101</t>
+          <t>MS-EV-201</t>
         </is>
       </c>
       <c r="O56" s="3" t="n"/>
@@ -3159,7 +3223,7 @@
     </row>
     <row r="57">
       <c r="B57" s="2" t="n">
-        <v>510</v>
+        <v>550</v>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
@@ -3173,17 +3237,17 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>온습도1 후 7일방치OCV</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="n">
-        <v>3.75</v>
-      </c>
+          <t>열충격1 후 △V  (24hr)</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="n"/>
       <c r="G57" s="2" t="n"/>
-      <c r="H57" s="2" t="n"/>
+      <c r="H57" s="2" t="n">
+        <v>0.035</v>
+      </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>≥ 3.75</t>
+          <t>≤ 0.035</t>
         </is>
       </c>
       <c r="J57" s="3" t="n"/>
@@ -3199,12 +3263,12 @@
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>상온 7일 방치</t>
+          <t>-30℃↔85℃ 50사이클</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>MS-EV-101</t>
+          <t>MS-EV-201</t>
         </is>
       </c>
       <c r="O57" s="3" t="n"/>
@@ -3212,7 +3276,7 @@
     </row>
     <row r="58">
       <c r="B58" s="2" t="n">
-        <v>520</v>
+        <v>560</v>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
@@ -3226,32 +3290,38 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>온습도1 후 한계평가</t>
+          <t>열충격1 후 △R</t>
         </is>
       </c>
       <c r="F58" s="2" t="n"/>
       <c r="G58" s="2" t="n"/>
-      <c r="H58" s="2" t="n"/>
-      <c r="I58" s="3" t="n"/>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>발화·폭발 없을 것</t>
-        </is>
-      </c>
-      <c r="K58" s="3" t="n"/>
+      <c r="H58" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>≤ 20</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="n"/>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>안전 항목</t>
+          <t>초기 IR 대비</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>MS-EV-901</t>
+          <t>MS-EV-201</t>
         </is>
       </c>
       <c r="O58" s="3" t="n"/>
@@ -3259,7 +3329,7 @@
     </row>
     <row r="59">
       <c r="B59" s="2" t="n">
-        <v>530</v>
+        <v>570</v>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
@@ -3273,19 +3343,25 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>온습도 후 해체</t>
+          <t>열충격1 후 △T  (직후두께) 3</t>
         </is>
       </c>
       <c r="F59" s="2" t="n"/>
       <c r="G59" s="2" t="n"/>
-      <c r="H59" s="2" t="n"/>
-      <c r="I59" s="3" t="n"/>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>음극 표면 리튬 석출 없을 것</t>
-        </is>
-      </c>
-      <c r="K59" s="3" t="n"/>
+      <c r="H59" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>≤ 8</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="n"/>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
           <t>A</t>
@@ -3293,12 +3369,12 @@
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>해체 분석</t>
+          <t>시험 직후 측정</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>MS-EV-902</t>
+          <t>MS-EV-201</t>
         </is>
       </c>
       <c r="O59" s="3" t="n"/>
@@ -3306,7 +3382,7 @@
     </row>
     <row r="60">
       <c r="B60" s="2" t="n">
-        <v>540</v>
+        <v>580</v>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
@@ -3320,23 +3396,23 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>열충격1 후 △V  (2hr)</t>
+          <t>열충격1 후 △T  (2hr두께) 3</t>
         </is>
       </c>
       <c r="F60" s="2" t="n"/>
       <c r="G60" s="2" t="n"/>
       <c r="H60" s="2" t="n">
-        <v>0.025</v>
+        <v>6</v>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>≤ 0.025</t>
+          <t>≤ 6</t>
         </is>
       </c>
       <c r="J60" s="3" t="n"/>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>%</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
@@ -3346,7 +3422,7 @@
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>-30℃↔85℃ 50사이클</t>
+          <t>2시간 후 측정</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
@@ -3359,7 +3435,7 @@
     </row>
     <row r="61">
       <c r="B61" s="2" t="n">
-        <v>550</v>
+        <v>590</v>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
@@ -3373,25 +3449,19 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>열충격1 후 △V  (24hr)</t>
+          <t>열충격1 후 외관</t>
         </is>
       </c>
       <c r="F61" s="2" t="n"/>
       <c r="G61" s="2" t="n"/>
-      <c r="H61" s="2" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="I61" s="3" t="inlineStr">
-        <is>
-          <t>≤ 0.035</t>
-        </is>
-      </c>
-      <c r="J61" s="3" t="n"/>
-      <c r="K61" s="3" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="H61" s="2" t="n"/>
+      <c r="I61" s="3" t="n"/>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>부풀음·누액·변색 없을 것</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="n"/>
       <c r="L61" s="3" t="inlineStr">
         <is>
           <t>A</t>
@@ -3399,7 +3469,7 @@
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>-30℃↔85℃ 50사이클</t>
+          <t>육안 검사</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
@@ -3412,7 +3482,7 @@
     </row>
     <row r="62">
       <c r="B62" s="2" t="n">
-        <v>560</v>
+        <v>600</v>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
@@ -3426,17 +3496,17 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>열충격1 후 △R</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="n"/>
+          <t>열충격1 후 용량(0.2C)</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>93</v>
+      </c>
       <c r="G62" s="2" t="n"/>
-      <c r="H62" s="2" t="n">
-        <v>20</v>
-      </c>
+      <c r="H62" s="2" t="n"/>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>≤ 20</t>
+          <t>≥ 93</t>
         </is>
       </c>
       <c r="J62" s="3" t="n"/>
@@ -3452,7 +3522,7 @@
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>초기 IR 대비</t>
+          <t>초기 용량 대비</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
@@ -3465,7 +3535,7 @@
     </row>
     <row r="63">
       <c r="B63" s="2" t="n">
-        <v>570</v>
+        <v>610</v>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
@@ -3479,17 +3549,17 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>열충격1 후 △T  (직후두께) 3</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="n"/>
+          <t>열충격1 후 용량(1.0C)</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>91</v>
+      </c>
       <c r="G63" s="2" t="n"/>
-      <c r="H63" s="2" t="n">
-        <v>8</v>
-      </c>
+      <c r="H63" s="2" t="n"/>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>≤ 8</t>
+          <t>≥ 91</t>
         </is>
       </c>
       <c r="J63" s="3" t="n"/>
@@ -3500,12 +3570,12 @@
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>시험 직후 측정</t>
+          <t>초기 용량 대비</t>
         </is>
       </c>
       <c r="N63" s="3" t="inlineStr">
@@ -3518,7 +3588,7 @@
     </row>
     <row r="64">
       <c r="B64" s="2" t="n">
-        <v>580</v>
+        <v>620</v>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
@@ -3532,23 +3602,23 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>열충격1 후 △T  (2hr두께) 3</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="n"/>
+          <t>열충격1 후 7일방치  OCV</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>3.72</v>
+      </c>
       <c r="G64" s="2" t="n"/>
-      <c r="H64" s="2" t="n">
-        <v>6</v>
-      </c>
+      <c r="H64" s="2" t="n"/>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>≤ 6</t>
+          <t>≥ 3.72</t>
         </is>
       </c>
       <c r="J64" s="3" t="n"/>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>V</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
@@ -3558,7 +3628,7 @@
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>2시간 후 측정</t>
+          <t>상온 7일 방치</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
@@ -3571,7 +3641,7 @@
     </row>
     <row r="65">
       <c r="B65" s="2" t="n">
-        <v>590</v>
+        <v>630</v>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
@@ -3585,7 +3655,7 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>열충격1 후 외관</t>
+          <t>열충격1 후 한계평가</t>
         </is>
       </c>
       <c r="F65" s="2" t="n"/>
@@ -3594,7 +3664,7 @@
       <c r="I65" s="3" t="n"/>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>부풀음·누액·변색 없을 것</t>
+          <t>발화·폭발 없을 것</t>
         </is>
       </c>
       <c r="K65" s="3" t="n"/>
@@ -3605,12 +3675,12 @@
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>육안 검사</t>
+          <t>안전 항목</t>
         </is>
       </c>
       <c r="N65" s="3" t="inlineStr">
         <is>
-          <t>MS-EV-201</t>
+          <t>MS-EV-901</t>
         </is>
       </c>
       <c r="O65" s="3" t="n"/>
@@ -3618,7 +3688,7 @@
     </row>
     <row r="66">
       <c r="B66" s="2" t="n">
-        <v>600</v>
+        <v>640</v>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
@@ -3632,38 +3702,32 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>열충격1 후 용량(0.2C)</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="n">
-        <v>93</v>
-      </c>
+          <t>열충격 후 해체</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="n"/>
       <c r="G66" s="2" t="n"/>
       <c r="H66" s="2" t="n"/>
-      <c r="I66" s="3" t="inlineStr">
-        <is>
-          <t>≥ 93</t>
-        </is>
-      </c>
-      <c r="J66" s="3" t="n"/>
-      <c r="K66" s="3" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
+      <c r="I66" s="3" t="n"/>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>음극 표면 리튬 석출 없을 것</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="n"/>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>초기 용량 대비</t>
+          <t>해체 분석</t>
         </is>
       </c>
       <c r="N66" s="3" t="inlineStr">
         <is>
-          <t>MS-EV-201</t>
+          <t>MS-EV-902</t>
         </is>
       </c>
       <c r="O66" s="3" t="n"/>
@@ -3671,7 +3735,7 @@
     </row>
     <row r="67">
       <c r="B67" s="2" t="n">
-        <v>610</v>
+        <v>650</v>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
@@ -3685,17 +3749,17 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>열충격1 후 용량(1.0C)</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="n">
-        <v>91</v>
-      </c>
+          <t>고온동작△R (2hr)</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="n"/>
       <c r="G67" s="2" t="n"/>
-      <c r="H67" s="2" t="n"/>
+      <c r="H67" s="2" t="n">
+        <v>18</v>
+      </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>≥ 91</t>
+          <t>≤ 18</t>
         </is>
       </c>
       <c r="J67" s="3" t="n"/>
@@ -3711,12 +3775,12 @@
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>초기 용량 대비</t>
+          <t>45℃ 동작</t>
         </is>
       </c>
       <c r="N67" s="3" t="inlineStr">
         <is>
-          <t>MS-EV-201</t>
+          <t>MS-EV-301</t>
         </is>
       </c>
       <c r="O67" s="3" t="n"/>
@@ -3724,7 +3788,7 @@
     </row>
     <row r="68">
       <c r="B68" s="2" t="n">
-        <v>620</v>
+        <v>660</v>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
@@ -3738,17 +3802,17 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>열충격1 후 7일방치  OCV</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="n">
-        <v>3.72</v>
-      </c>
+          <t>고온동작△V (2hr)</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="n"/>
       <c r="G68" s="2" t="n"/>
-      <c r="H68" s="2" t="n"/>
+      <c r="H68" s="2" t="n">
+        <v>0.022</v>
+      </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>≥ 3.72</t>
+          <t>≤ 0.022</t>
         </is>
       </c>
       <c r="J68" s="3" t="n"/>
@@ -3764,12 +3828,12 @@
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>상온 7일 방치</t>
+          <t>45℃ 동작</t>
         </is>
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
-          <t>MS-EV-201</t>
+          <t>MS-EV-301</t>
         </is>
       </c>
       <c r="O68" s="3" t="n"/>
@@ -3777,7 +3841,7 @@
     </row>
     <row r="69">
       <c r="B69" s="2" t="n">
-        <v>630</v>
+        <v>670</v>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
@@ -3791,19 +3855,25 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>열충격1 후 한계평가</t>
+          <t>고온동작△V (24hr)</t>
         </is>
       </c>
       <c r="F69" s="2" t="n"/>
       <c r="G69" s="2" t="n"/>
-      <c r="H69" s="2" t="n"/>
-      <c r="I69" s="3" t="n"/>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>발화·폭발 없을 것</t>
-        </is>
-      </c>
-      <c r="K69" s="3" t="n"/>
+      <c r="H69" s="2" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>≤ 0.032</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="n"/>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
           <t>A</t>
@@ -3811,12 +3881,12 @@
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>안전 항목</t>
+          <t>45℃ 동작</t>
         </is>
       </c>
       <c r="N69" s="3" t="inlineStr">
         <is>
-          <t>MS-EV-901</t>
+          <t>MS-EV-301</t>
         </is>
       </c>
       <c r="O69" s="3" t="n"/>
@@ -3824,7 +3894,7 @@
     </row>
     <row r="70">
       <c r="B70" s="2" t="n">
-        <v>640</v>
+        <v>680</v>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
@@ -3838,19 +3908,25 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>열충격 후 해체</t>
+          <t>고온동작△T (2hr) 3</t>
         </is>
       </c>
       <c r="F70" s="2" t="n"/>
       <c r="G70" s="2" t="n"/>
-      <c r="H70" s="2" t="n"/>
-      <c r="I70" s="3" t="n"/>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>음극 표면 리튬 석출 없을 것</t>
-        </is>
-      </c>
-      <c r="K70" s="3" t="n"/>
+      <c r="H70" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>≤ 7</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="n"/>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
           <t>A</t>
@@ -3858,12 +3934,12 @@
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>해체 분석</t>
+          <t>초기 두께 대비</t>
         </is>
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
-          <t>MS-EV-902</t>
+          <t>MS-EV-301</t>
         </is>
       </c>
       <c r="O70" s="3" t="n"/>
@@ -3871,7 +3947,7 @@
     </row>
     <row r="71">
       <c r="B71" s="2" t="n">
-        <v>650</v>
+        <v>690</v>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
@@ -3885,17 +3961,17 @@
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>고온동작△R (2hr)</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="n"/>
+          <t>고온동작 후  용량(0.2C)</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>94</v>
+      </c>
       <c r="G71" s="2" t="n"/>
-      <c r="H71" s="2" t="n">
-        <v>18</v>
-      </c>
+      <c r="H71" s="2" t="n"/>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>≤ 18</t>
+          <t>≥ 94</t>
         </is>
       </c>
       <c r="J71" s="3" t="n"/>
@@ -3911,7 +3987,7 @@
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
-          <t>45℃ 동작</t>
+          <t>초기 용량 대비</t>
         </is>
       </c>
       <c r="N71" s="3" t="inlineStr">
@@ -3924,7 +4000,7 @@
     </row>
     <row r="72">
       <c r="B72" s="2" t="n">
-        <v>660</v>
+        <v>700</v>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
@@ -3938,33 +4014,33 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>고온동작△V (2hr)</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="n"/>
+          <t>고온동작 후 용량(1.0C)</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>92</v>
+      </c>
       <c r="G72" s="2" t="n"/>
-      <c r="H72" s="2" t="n">
-        <v>0.022</v>
-      </c>
+      <c r="H72" s="2" t="n"/>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>≤ 0.022</t>
+          <t>≥ 92</t>
         </is>
       </c>
       <c r="J72" s="3" t="n"/>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>%</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>45℃ 동작</t>
+          <t>초기 용량 대비</t>
         </is>
       </c>
       <c r="N72" s="3" t="inlineStr">
@@ -3977,7 +4053,7 @@
     </row>
     <row r="73">
       <c r="B73" s="2" t="n">
-        <v>670</v>
+        <v>710</v>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
@@ -3991,38 +4067,38 @@
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>고온동작△V (24hr)</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="n"/>
+          <t>Dyne Pen 검사</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>38</v>
+      </c>
       <c r="G73" s="2" t="n"/>
-      <c r="H73" s="2" t="n">
-        <v>0.032</v>
-      </c>
+      <c r="H73" s="2" t="n"/>
       <c r="I73" s="3" t="inlineStr">
         <is>
-          <t>≤ 0.032</t>
+          <t>≥ 38</t>
         </is>
       </c>
       <c r="J73" s="3" t="n"/>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>dyn/cm</t>
         </is>
       </c>
       <c r="L73" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
-          <t>45℃ 동작</t>
+          <t>파우치 표면 젖음성</t>
         </is>
       </c>
       <c r="N73" s="3" t="inlineStr">
         <is>
-          <t>MS-EV-301</t>
+          <t>MS-SF-001</t>
         </is>
       </c>
       <c r="O73" s="3" t="n"/>
@@ -4030,7 +4106,7 @@
     </row>
     <row r="74">
       <c r="B74" s="2" t="n">
-        <v>680</v>
+        <v>720</v>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
@@ -4039,43 +4115,47 @@
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>환경특성</t>
+          <t>Mass ILT/PRT</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>고온동작△T (2hr) 3</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="n"/>
-      <c r="G74" s="2" t="n"/>
+          <t>OCV</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>3.83</v>
+      </c>
       <c r="H74" s="2" t="n">
-        <v>7</v>
+        <v>3.86</v>
       </c>
       <c r="I74" s="3" t="inlineStr">
         <is>
-          <t>≤ 7</t>
+          <t>3.83 ± 0.03</t>
         </is>
       </c>
       <c r="J74" s="3" t="n"/>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>V</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>초기 두께 대비</t>
+          <t>양산 전수 검사</t>
         </is>
       </c>
       <c r="N74" s="3" t="inlineStr">
         <is>
-          <t>MS-EV-301</t>
+          <t>MS-PRT-001</t>
         </is>
       </c>
       <c r="O74" s="3" t="n"/>
@@ -4083,7 +4163,7 @@
     </row>
     <row r="75">
       <c r="B75" s="2" t="n">
-        <v>690</v>
+        <v>730</v>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
@@ -4092,28 +4172,28 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>환경특성</t>
+          <t>Mass ILT/PRT</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>고온동작 후  용량(0.2C)</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="n">
-        <v>94</v>
-      </c>
+          <t>△IR</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="n"/>
       <c r="G75" s="2" t="n"/>
-      <c r="H75" s="2" t="n"/>
+      <c r="H75" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>≥ 94</t>
+          <t>≤ 3</t>
         </is>
       </c>
       <c r="J75" s="3" t="n"/>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>mΩ</t>
         </is>
       </c>
       <c r="L75" s="3" t="inlineStr">
@@ -4123,12 +4203,12 @@
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
-          <t>초기 용량 대비</t>
+          <t>Lot 내 편차</t>
         </is>
       </c>
       <c r="N75" s="3" t="inlineStr">
         <is>
-          <t>MS-EV-301</t>
+          <t>MS-PRT-001</t>
         </is>
       </c>
       <c r="O75" s="3" t="n"/>
@@ -4136,7 +4216,7 @@
     </row>
     <row r="76">
       <c r="B76" s="2" t="n">
-        <v>700</v>
+        <v>740</v>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
@@ -4145,43 +4225,43 @@
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>환경특성</t>
+          <t>Mass ILT/PRT</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>고온동작 후 용량(1.0C)</t>
+          <t>Short</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G76" s="2" t="n"/>
       <c r="H76" s="2" t="n"/>
       <c r="I76" s="3" t="inlineStr">
         <is>
-          <t>≥ 92</t>
+          <t>≥ 100</t>
         </is>
       </c>
       <c r="J76" s="3" t="n"/>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>MΩ</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t>초기 용량 대비</t>
+          <t>500V 절연 저항</t>
         </is>
       </c>
       <c r="N76" s="3" t="inlineStr">
         <is>
-          <t>MS-EV-301</t>
+          <t>MS-PRT-002</t>
         </is>
       </c>
       <c r="O76" s="3" t="n"/>
@@ -4189,7 +4269,7 @@
     </row>
     <row r="77">
       <c r="B77" s="2" t="n">
-        <v>710</v>
+        <v>750</v>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
@@ -4198,43 +4278,43 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>환경특성</t>
+          <t>Mass ILT/PRT</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>Dyne Pen 검사</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="n">
-        <v>38</v>
-      </c>
+          <t>Swelling</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="n"/>
       <c r="G77" s="2" t="n"/>
-      <c r="H77" s="2" t="n"/>
+      <c r="H77" s="2" t="n">
+        <v>0.1</v>
+      </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>≥ 38</t>
+          <t>≤ 0.1</t>
         </is>
       </c>
       <c r="J77" s="3" t="n"/>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>dyn/cm</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
-          <t>파우치 표면 젖음성</t>
+          <t>검사 전후 두께차</t>
         </is>
       </c>
       <c r="N77" s="3" t="inlineStr">
         <is>
-          <t>MS-SF-001</t>
+          <t>MS-PRT-003</t>
         </is>
       </c>
       <c r="O77" s="3" t="n"/>
@@ -4242,7 +4322,7 @@
     </row>
     <row r="78">
       <c r="B78" s="2" t="n">
-        <v>720</v>
+        <v>760</v>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
@@ -4251,47 +4331,45 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Mass ILT/PRT</t>
+          <t>전기적 특성</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>OCV</t>
+          <t>표준용량</t>
         </is>
       </c>
       <c r="F78" s="2" t="n">
-        <v>3.8</v>
+        <v>1150</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="H78" s="2" t="n">
-        <v>3.86</v>
-      </c>
+        <v>1180</v>
+      </c>
+      <c r="H78" s="2" t="n"/>
       <c r="I78" s="3" t="inlineStr">
         <is>
-          <t>3.83 ± 0.03</t>
+          <t>≥ 1150 (typ. 1180)</t>
         </is>
       </c>
       <c r="J78" s="3" t="n"/>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>mAh</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>양산 전수 검사</t>
+          <t>0.2C 방전</t>
         </is>
       </c>
       <c r="N78" s="3" t="inlineStr">
         <is>
-          <t>MS-PRT-001</t>
+          <t>MS-CP-001</t>
         </is>
       </c>
       <c r="O78" s="3" t="n"/>
@@ -4299,7 +4377,7 @@
     </row>
     <row r="79">
       <c r="B79" s="2" t="n">
-        <v>730</v>
+        <v>770</v>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
@@ -4308,28 +4386,30 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>Mass ILT/PRT</t>
+          <t>전기적 특성</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>△IR</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="n"/>
-      <c r="G79" s="2" t="n"/>
-      <c r="H79" s="2" t="n">
-        <v>3</v>
-      </c>
+          <t>출하용량</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>340</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>355</v>
+      </c>
+      <c r="H79" s="2" t="n"/>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>≤ 3</t>
+          <t>≥ 340 (typ. 355)</t>
         </is>
       </c>
       <c r="J79" s="3" t="n"/>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>mΩ</t>
+          <t>mAh</t>
         </is>
       </c>
       <c r="L79" s="3" t="inlineStr">
@@ -4339,12 +4419,12 @@
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
-          <t>Lot 내 편차</t>
+          <t>출하 SOC 30% 기준</t>
         </is>
       </c>
       <c r="N79" s="3" t="inlineStr">
         <is>
-          <t>MS-PRT-001</t>
+          <t>MS-CP-002</t>
         </is>
       </c>
       <c r="O79" s="3" t="n"/>
@@ -4352,7 +4432,7 @@
     </row>
     <row r="80">
       <c r="B80" s="2" t="n">
-        <v>740</v>
+        <v>780</v>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
@@ -4361,43 +4441,43 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>Mass ILT/PRT</t>
+          <t>전기적 특성</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>Short</t>
+          <t>출하검사용량2</t>
         </is>
       </c>
       <c r="F80" s="2" t="n">
-        <v>100</v>
+        <v>1140</v>
       </c>
       <c r="G80" s="2" t="n"/>
       <c r="H80" s="2" t="n"/>
       <c r="I80" s="3" t="inlineStr">
         <is>
-          <t>≥ 100</t>
+          <t>≥ 1140</t>
         </is>
       </c>
       <c r="J80" s="3" t="n"/>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>MΩ</t>
+          <t>mAh</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>500V 절연 저항</t>
+          <t>샘플 검사</t>
         </is>
       </c>
       <c r="N80" s="3" t="inlineStr">
         <is>
-          <t>MS-PRT-002</t>
+          <t>MS-CP-003</t>
         </is>
       </c>
       <c r="O80" s="3" t="n"/>
@@ -4405,7 +4485,7 @@
     </row>
     <row r="81">
       <c r="B81" s="2" t="n">
-        <v>750</v>
+        <v>790</v>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
@@ -4414,28 +4494,28 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Mass ILT/PRT</t>
+          <t>전기적 특성</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>Swelling</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="n"/>
+          <t>정격용량</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>1150</v>
+      </c>
       <c r="G81" s="2" t="n"/>
-      <c r="H81" s="2" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="H81" s="2" t="n"/>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>≤ 0.1</t>
+          <t>≥ 1150</t>
         </is>
       </c>
       <c r="J81" s="3" t="n"/>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>mAh</t>
         </is>
       </c>
       <c r="L81" s="3" t="inlineStr">
@@ -4445,12 +4525,12 @@
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
-          <t>검사 전후 두께차</t>
+          <t>기본사양 30번과 동일 항목</t>
         </is>
       </c>
       <c r="N81" s="3" t="inlineStr">
         <is>
-          <t>MS-PRT-003</t>
+          <t>MS-CP-001</t>
         </is>
       </c>
       <c r="O81" s="3" t="n"/>
@@ -4458,7 +4538,7 @@
     </row>
     <row r="82">
       <c r="B82" s="2" t="n">
-        <v>760</v>
+        <v>800</v>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
@@ -4472,19 +4552,17 @@
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>표준용량</t>
+          <t>GB/T용량 (1.0C충전)</t>
         </is>
       </c>
       <c r="F82" s="2" t="n">
-        <v>1150</v>
-      </c>
-      <c r="G82" s="2" t="n">
-        <v>1180</v>
-      </c>
+        <v>1130</v>
+      </c>
+      <c r="G82" s="2" t="n"/>
       <c r="H82" s="2" t="n"/>
       <c r="I82" s="3" t="inlineStr">
         <is>
-          <t>≥ 1150 (typ. 1180)</t>
+          <t>≥ 1130</t>
         </is>
       </c>
       <c r="J82" s="3" t="n"/>
@@ -4495,17 +4573,17 @@
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>0.2C 방전</t>
+          <t>GB/T 18287 준용</t>
         </is>
       </c>
       <c r="N82" s="3" t="inlineStr">
         <is>
-          <t>MS-CP-001</t>
+          <t>GB/T 18287</t>
         </is>
       </c>
       <c r="O82" s="3" t="n"/>
@@ -4513,7 +4591,7 @@
     </row>
     <row r="83">
       <c r="B83" s="2" t="n">
-        <v>770</v>
+        <v>810</v>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
@@ -4527,25 +4605,23 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>출하용량</t>
+          <t>율별방전 : 0.2C</t>
         </is>
       </c>
       <c r="F83" s="2" t="n">
-        <v>340</v>
-      </c>
-      <c r="G83" s="2" t="n">
-        <v>355</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="G83" s="2" t="n"/>
       <c r="H83" s="2" t="n"/>
       <c r="I83" s="3" t="inlineStr">
         <is>
-          <t>≥ 340 (typ. 355)</t>
+          <t>≥ 99</t>
         </is>
       </c>
       <c r="J83" s="3" t="n"/>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>mAh</t>
+          <t>%</t>
         </is>
       </c>
       <c r="L83" s="3" t="inlineStr">
@@ -4555,12 +4631,12 @@
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
-          <t>출하 SOC 30% 기준</t>
+          <t>표준용량 대비</t>
         </is>
       </c>
       <c r="N83" s="3" t="inlineStr">
         <is>
-          <t>MS-CP-002</t>
+          <t>MS-RT-001</t>
         </is>
       </c>
       <c r="O83" s="3" t="n"/>
@@ -4568,7 +4644,7 @@
     </row>
     <row r="84">
       <c r="B84" s="2" t="n">
-        <v>780</v>
+        <v>820</v>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
@@ -4582,23 +4658,23 @@
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>출하검사용량2</t>
+          <t>율별방전 : 0.5C</t>
         </is>
       </c>
       <c r="F84" s="2" t="n">
-        <v>1140</v>
+        <v>97</v>
       </c>
       <c r="G84" s="2" t="n"/>
       <c r="H84" s="2" t="n"/>
       <c r="I84" s="3" t="inlineStr">
         <is>
-          <t>≥ 1140</t>
+          <t>≥ 97</t>
         </is>
       </c>
       <c r="J84" s="3" t="n"/>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>mAh</t>
+          <t>%</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr">
@@ -4608,12 +4684,12 @@
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>샘플 검사</t>
+          <t>표준용량 대비</t>
         </is>
       </c>
       <c r="N84" s="3" t="inlineStr">
         <is>
-          <t>MS-CP-003</t>
+          <t>MS-RT-001</t>
         </is>
       </c>
       <c r="O84" s="3" t="n"/>
@@ -4621,7 +4697,7 @@
     </row>
     <row r="85">
       <c r="B85" s="2" t="n">
-        <v>790</v>
+        <v>830</v>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
@@ -4635,38 +4711,38 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>정격용량</t>
+          <t>율별방전 : 1.0C</t>
         </is>
       </c>
       <c r="F85" s="2" t="n">
-        <v>1150</v>
+        <v>95</v>
       </c>
       <c r="G85" s="2" t="n"/>
       <c r="H85" s="2" t="n"/>
       <c r="I85" s="3" t="inlineStr">
         <is>
-          <t>≥ 1150</t>
+          <t>≥ 95</t>
         </is>
       </c>
       <c r="J85" s="3" t="n"/>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>mAh</t>
+          <t>%</t>
         </is>
       </c>
       <c r="L85" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
-          <t>기본사양 30번과 동일 항목</t>
+          <t>표준용량 대비</t>
         </is>
       </c>
       <c r="N85" s="3" t="inlineStr">
         <is>
-          <t>MS-CP-001</t>
+          <t>MS-RT-001</t>
         </is>
       </c>
       <c r="O85" s="3" t="n"/>
@@ -4674,7 +4750,7 @@
     </row>
     <row r="86">
       <c r="B86" s="2" t="n">
-        <v>800</v>
+        <v>840</v>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
@@ -4688,23 +4764,23 @@
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>GB/T용량 (1.0C충전)</t>
+          <t>온도별방전(3.0V) :  -20℃</t>
         </is>
       </c>
       <c r="F86" s="2" t="n">
-        <v>1130</v>
+        <v>55</v>
       </c>
       <c r="G86" s="2" t="n"/>
       <c r="H86" s="2" t="n"/>
       <c r="I86" s="3" t="inlineStr">
         <is>
-          <t>≥ 1130</t>
+          <t>≥ 55</t>
         </is>
       </c>
       <c r="J86" s="3" t="n"/>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>mAh</t>
+          <t>%</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr">
@@ -4714,12 +4790,12 @@
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
-          <t>GB/T 18287 준용</t>
+          <t>종지 3.0V</t>
         </is>
       </c>
       <c r="N86" s="3" t="inlineStr">
         <is>
-          <t>GB/T 18287</t>
+          <t>MS-RT-002</t>
         </is>
       </c>
       <c r="O86" s="3" t="n"/>
@@ -4727,7 +4803,7 @@
     </row>
     <row r="87">
       <c r="B87" s="2" t="n">
-        <v>810</v>
+        <v>850</v>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
@@ -4741,17 +4817,17 @@
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>율별방전 : 0.2C</t>
+          <t>온도별방전(3.0V) :  -10℃</t>
         </is>
       </c>
       <c r="F87" s="2" t="n">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="G87" s="2" t="n"/>
       <c r="H87" s="2" t="n"/>
       <c r="I87" s="3" t="inlineStr">
         <is>
-          <t>≥ 99</t>
+          <t>≥ 70</t>
         </is>
       </c>
       <c r="J87" s="3" t="n"/>
@@ -4767,12 +4843,12 @@
       </c>
       <c r="M87" s="3" t="inlineStr">
         <is>
-          <t>표준용량 대비</t>
+          <t>종지 3.0V</t>
         </is>
       </c>
       <c r="N87" s="3" t="inlineStr">
         <is>
-          <t>MS-RT-001</t>
+          <t>MS-RT-002</t>
         </is>
       </c>
       <c r="O87" s="3" t="n"/>
@@ -4780,7 +4856,7 @@
     </row>
     <row r="88">
       <c r="B88" s="2" t="n">
-        <v>820</v>
+        <v>860</v>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
@@ -4794,17 +4870,17 @@
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>율별방전 : 0.5C</t>
+          <t>온도별방전(3.0V) :  55℃</t>
         </is>
       </c>
       <c r="F88" s="2" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G88" s="2" t="n"/>
       <c r="H88" s="2" t="n"/>
       <c r="I88" s="3" t="inlineStr">
         <is>
-          <t>≥ 97</t>
+          <t>≥ 96</t>
         </is>
       </c>
       <c r="J88" s="3" t="n"/>
@@ -4820,12 +4896,12 @@
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>표준용량 대비</t>
+          <t>종지 3.0V</t>
         </is>
       </c>
       <c r="N88" s="3" t="inlineStr">
         <is>
-          <t>MS-RT-001</t>
+          <t>MS-RT-002</t>
         </is>
       </c>
       <c r="O88" s="3" t="n"/>
@@ -4833,7 +4909,7 @@
     </row>
     <row r="89">
       <c r="B89" s="2" t="n">
-        <v>830</v>
+        <v>870</v>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
@@ -4847,17 +4923,17 @@
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>율별방전 : 1.0C</t>
+          <t>만충전 상온 28일 방치  (잔존용량)</t>
         </is>
       </c>
       <c r="F89" s="2" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G89" s="2" t="n"/>
       <c r="H89" s="2" t="n"/>
       <c r="I89" s="3" t="inlineStr">
         <is>
-          <t>≥ 95</t>
+          <t>≥ 90</t>
         </is>
       </c>
       <c r="J89" s="3" t="n"/>
@@ -4873,12 +4949,12 @@
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
-          <t>표준용량 대비</t>
+          <t>만충전 후 방치</t>
         </is>
       </c>
       <c r="N89" s="3" t="inlineStr">
         <is>
-          <t>MS-RT-001</t>
+          <t>MS-ST-001</t>
         </is>
       </c>
       <c r="O89" s="3" t="n"/>
@@ -4886,7 +4962,7 @@
     </row>
     <row r="90">
       <c r="B90" s="2" t="n">
-        <v>840</v>
+        <v>880</v>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
@@ -4900,17 +4976,17 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>온도별방전(3.0V) :  -20℃</t>
+          <t>만충전 상온 28일 방치  (회복용량)</t>
         </is>
       </c>
       <c r="F90" s="2" t="n">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="G90" s="2" t="n"/>
       <c r="H90" s="2" t="n"/>
       <c r="I90" s="3" t="inlineStr">
         <is>
-          <t>≥ 55</t>
+          <t>≥ 95</t>
         </is>
       </c>
       <c r="J90" s="3" t="n"/>
@@ -4926,12 +5002,12 @@
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
-          <t>종지 3.0V</t>
+          <t>재충전 후 측정</t>
         </is>
       </c>
       <c r="N90" s="3" t="inlineStr">
         <is>
-          <t>MS-RT-002</t>
+          <t>MS-ST-001</t>
         </is>
       </c>
       <c r="O90" s="3" t="n"/>
@@ -4939,7 +5015,7 @@
     </row>
     <row r="91">
       <c r="B91" s="2" t="n">
-        <v>850</v>
+        <v>890</v>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
@@ -4953,17 +5029,17 @@
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>온도별방전(3.0V) :  -10℃</t>
+          <t>출하충전 상온 12달  방치(잔존용량)</t>
         </is>
       </c>
       <c r="F91" s="2" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="G91" s="2" t="n"/>
       <c r="H91" s="2" t="n"/>
       <c r="I91" s="3" t="inlineStr">
         <is>
-          <t>≥ 70</t>
+          <t>≥ 85</t>
         </is>
       </c>
       <c r="J91" s="3" t="n"/>
@@ -4979,12 +5055,12 @@
       </c>
       <c r="M91" s="3" t="inlineStr">
         <is>
-          <t>종지 3.0V</t>
+          <t>출하 SOC 기준</t>
         </is>
       </c>
       <c r="N91" s="3" t="inlineStr">
         <is>
-          <t>MS-RT-002</t>
+          <t>MS-ST-002</t>
         </is>
       </c>
       <c r="O91" s="3" t="n"/>
@@ -4992,7 +5068,7 @@
     </row>
     <row r="92">
       <c r="B92" s="2" t="n">
-        <v>860</v>
+        <v>900</v>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
@@ -5006,17 +5082,17 @@
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>온도별방전(3.0V) :  55℃</t>
+          <t>출하충전 고온(45℃) 60일 방치 (잔존용량)</t>
         </is>
       </c>
       <c r="F92" s="2" t="n">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="G92" s="2" t="n"/>
       <c r="H92" s="2" t="n"/>
       <c r="I92" s="3" t="inlineStr">
         <is>
-          <t>≥ 96</t>
+          <t>≥ 80</t>
         </is>
       </c>
       <c r="J92" s="3" t="n"/>
@@ -5032,12 +5108,12 @@
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
-          <t>종지 3.0V</t>
+          <t>고온 가속</t>
         </is>
       </c>
       <c r="N92" s="3" t="inlineStr">
         <is>
-          <t>MS-RT-002</t>
+          <t>MS-ST-003</t>
         </is>
       </c>
       <c r="O92" s="3" t="n"/>
@@ -5045,7 +5121,7 @@
     </row>
     <row r="93">
       <c r="B93" s="2" t="n">
-        <v>870</v>
+        <v>910</v>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
@@ -5059,17 +5135,17 @@
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>만충전 상온 28일 방치  (잔존용량)</t>
+          <t>출하충전상온  1달방치(회복용량)</t>
         </is>
       </c>
       <c r="F93" s="2" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="G93" s="2" t="n"/>
       <c r="H93" s="2" t="n"/>
       <c r="I93" s="3" t="inlineStr">
         <is>
-          <t>≥ 90</t>
+          <t>≥ 97</t>
         </is>
       </c>
       <c r="J93" s="3" t="n"/>
@@ -5080,17 +5156,17 @@
       </c>
       <c r="L93" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M93" s="3" t="inlineStr">
         <is>
-          <t>만충전 후 방치</t>
+          <t>재충전 후 측정</t>
         </is>
       </c>
       <c r="N93" s="3" t="inlineStr">
         <is>
-          <t>MS-ST-001</t>
+          <t>MS-ST-002</t>
         </is>
       </c>
       <c r="O93" s="3" t="n"/>
@@ -5098,7 +5174,7 @@
     </row>
     <row r="94">
       <c r="B94" s="2" t="n">
-        <v>880</v>
+        <v>920</v>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
@@ -5112,17 +5188,17 @@
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>만충전 상온 28일 방치  (회복용량)</t>
+          <t>출하충전상온  2달방치(회복용량)</t>
         </is>
       </c>
       <c r="F94" s="2" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G94" s="2" t="n"/>
       <c r="H94" s="2" t="n"/>
       <c r="I94" s="3" t="inlineStr">
         <is>
-          <t>≥ 95</t>
+          <t>≥ 96</t>
         </is>
       </c>
       <c r="J94" s="3" t="n"/>
@@ -5133,7 +5209,7 @@
       </c>
       <c r="L94" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M94" s="3" t="inlineStr">
@@ -5143,7 +5219,7 @@
       </c>
       <c r="N94" s="3" t="inlineStr">
         <is>
-          <t>MS-ST-001</t>
+          <t>MS-ST-002</t>
         </is>
       </c>
       <c r="O94" s="3" t="n"/>
@@ -5151,7 +5227,7 @@
     </row>
     <row r="95">
       <c r="B95" s="2" t="n">
-        <v>890</v>
+        <v>930</v>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
@@ -5165,17 +5241,17 @@
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>출하충전 상온 12달  방치(잔존용량)</t>
+          <t>출하충전상온 3달방치(회복용량)</t>
         </is>
       </c>
       <c r="F95" s="2" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="G95" s="2" t="n"/>
       <c r="H95" s="2" t="n"/>
       <c r="I95" s="3" t="inlineStr">
         <is>
-          <t>≥ 85</t>
+          <t>≥ 95</t>
         </is>
       </c>
       <c r="J95" s="3" t="n"/>
@@ -5186,12 +5262,12 @@
       </c>
       <c r="L95" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M95" s="3" t="inlineStr">
         <is>
-          <t>출하 SOC 기준</t>
+          <t>재충전 후 측정</t>
         </is>
       </c>
       <c r="N95" s="3" t="inlineStr">
@@ -5204,7 +5280,7 @@
     </row>
     <row r="96">
       <c r="B96" s="2" t="n">
-        <v>900</v>
+        <v>940</v>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
@@ -5218,17 +5294,17 @@
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>출하충전 고온(45℃) 60일 방치 (잔존용량)</t>
+          <t>출하충전상온  6달방치(회복용량)</t>
         </is>
       </c>
       <c r="F96" s="2" t="n">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G96" s="2" t="n"/>
       <c r="H96" s="2" t="n"/>
       <c r="I96" s="3" t="inlineStr">
         <is>
-          <t>≥ 80</t>
+          <t>≥ 93</t>
         </is>
       </c>
       <c r="J96" s="3" t="n"/>
@@ -5239,17 +5315,17 @@
       </c>
       <c r="L96" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M96" s="3" t="inlineStr">
         <is>
-          <t>고온 가속</t>
+          <t>재충전 후 측정</t>
         </is>
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
-          <t>MS-ST-003</t>
+          <t>MS-ST-002</t>
         </is>
       </c>
       <c r="O96" s="3" t="n"/>
@@ -5257,7 +5333,7 @@
     </row>
     <row r="97">
       <c r="B97" s="2" t="n">
-        <v>910</v>
+        <v>950</v>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
@@ -5271,17 +5347,17 @@
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>출하충전상온  1달방치(회복용량)</t>
+          <t>1개월 출충(선박심도)  방치 후 용량측정(GB/T)</t>
         </is>
       </c>
       <c r="F97" s="2" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G97" s="2" t="n"/>
       <c r="H97" s="2" t="n"/>
       <c r="I97" s="3" t="inlineStr">
         <is>
-          <t>≥ 97</t>
+          <t>≥ 96</t>
         </is>
       </c>
       <c r="J97" s="3" t="n"/>
@@ -5297,12 +5373,12 @@
       </c>
       <c r="M97" s="3" t="inlineStr">
         <is>
-          <t>재충전 후 측정</t>
+          <t>선박 수송 조건</t>
         </is>
       </c>
       <c r="N97" s="3" t="inlineStr">
         <is>
-          <t>MS-ST-002</t>
+          <t>GB/T 18287</t>
         </is>
       </c>
       <c r="O97" s="3" t="n"/>
@@ -5310,7 +5386,7 @@
     </row>
     <row r="98">
       <c r="B98" s="2" t="n">
-        <v>920</v>
+        <v>960</v>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
@@ -5324,17 +5400,17 @@
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>출하충전상온  2달방치(회복용량)</t>
+          <t>2개월 출충(선박심도)  방치 후 용량측정(GB/T)</t>
         </is>
       </c>
       <c r="F98" s="2" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G98" s="2" t="n"/>
       <c r="H98" s="2" t="n"/>
       <c r="I98" s="3" t="inlineStr">
         <is>
-          <t>≥ 96</t>
+          <t>≥ 95</t>
         </is>
       </c>
       <c r="J98" s="3" t="n"/>
@@ -5350,12 +5426,12 @@
       </c>
       <c r="M98" s="3" t="inlineStr">
         <is>
-          <t>재충전 후 측정</t>
+          <t>선박 수송 조건</t>
         </is>
       </c>
       <c r="N98" s="3" t="inlineStr">
         <is>
-          <t>MS-ST-002</t>
+          <t>GB/T 18287</t>
         </is>
       </c>
       <c r="O98" s="3" t="n"/>
@@ -5363,7 +5439,7 @@
     </row>
     <row r="99">
       <c r="B99" s="2" t="n">
-        <v>930</v>
+        <v>970</v>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
@@ -5377,17 +5453,17 @@
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>출하충전상온 3달방치(회복용량)</t>
+          <t>3개월 출충(선박심도) 방치 후 용량측정(GB/T)</t>
         </is>
       </c>
       <c r="F99" s="2" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G99" s="2" t="n"/>
       <c r="H99" s="2" t="n"/>
       <c r="I99" s="3" t="inlineStr">
         <is>
-          <t>≥ 95</t>
+          <t>≥ 94</t>
         </is>
       </c>
       <c r="J99" s="3" t="n"/>
@@ -5403,12 +5479,12 @@
       </c>
       <c r="M99" s="3" t="inlineStr">
         <is>
-          <t>재충전 후 측정</t>
+          <t>선박 수송 조건</t>
         </is>
       </c>
       <c r="N99" s="3" t="inlineStr">
         <is>
-          <t>MS-ST-002</t>
+          <t>GB/T 18287</t>
         </is>
       </c>
       <c r="O99" s="3" t="n"/>
@@ -5416,7 +5492,7 @@
     </row>
     <row r="100">
       <c r="B100" s="2" t="n">
-        <v>940</v>
+        <v>980</v>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
@@ -5430,17 +5506,17 @@
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>출하충전상온  6달방치(회복용량)</t>
+          <t>6개월 출충(선박심도)  방치 후 용량측정(GB/T)</t>
         </is>
       </c>
       <c r="F100" s="2" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G100" s="2" t="n"/>
       <c r="H100" s="2" t="n"/>
       <c r="I100" s="3" t="inlineStr">
         <is>
-          <t>≥ 93</t>
+          <t>≥ 92</t>
         </is>
       </c>
       <c r="J100" s="3" t="n"/>
@@ -5456,12 +5532,12 @@
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
-          <t>재충전 후 측정</t>
+          <t>선박 수송 조건</t>
         </is>
       </c>
       <c r="N100" s="3" t="inlineStr">
         <is>
-          <t>MS-ST-002</t>
+          <t>GB/T 18287</t>
         </is>
       </c>
       <c r="O100" s="3" t="n"/>
@@ -5469,7 +5545,7 @@
     </row>
     <row r="101">
       <c r="B101" s="2" t="n">
-        <v>950</v>
+        <v>990</v>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
@@ -5483,17 +5559,17 @@
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>1개월 출충(선박심도)  방치 후 용량측정(GB/T)</t>
+          <t>12개월 출충(선박심도) 방치 후 용량측정(GB/T)</t>
         </is>
       </c>
       <c r="F101" s="2" t="n">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="G101" s="2" t="n"/>
       <c r="H101" s="2" t="n"/>
       <c r="I101" s="3" t="inlineStr">
         <is>
-          <t>≥ 96</t>
+          <t>≥ 89</t>
         </is>
       </c>
       <c r="J101" s="3" t="n"/>
@@ -5522,7 +5598,7 @@
     </row>
     <row r="102">
       <c r="B102" s="2" t="n">
-        <v>960</v>
+        <v>1000</v>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
@@ -5531,259 +5607,47 @@
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>전기적 특성</t>
+          <t>고온방치특성</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>2개월 출충(선박심도)  방치 후 용량측정(GB/T)</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="n">
-        <v>95</v>
-      </c>
+          <t>고온연속충전 두께 3</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="n"/>
       <c r="G102" s="2" t="n"/>
-      <c r="H102" s="2" t="n"/>
+      <c r="H102" s="2" t="n">
+        <v>5.2</v>
+      </c>
       <c r="I102" s="3" t="inlineStr">
         <is>
-          <t>≥ 95</t>
+          <t>≤ 5.2</t>
         </is>
       </c>
       <c r="J102" s="3" t="n"/>
       <c r="K102" s="3" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="L102" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M102" s="3" t="inlineStr">
         <is>
-          <t>선박 수송 조건</t>
+          <t>60℃ 7일 연속 충전</t>
         </is>
       </c>
       <c r="N102" s="3" t="inlineStr">
         <is>
-          <t>GB/T 18287</t>
+          <t>MS-EV-401</t>
         </is>
       </c>
       <c r="O102" s="3" t="n"/>
       <c r="P102" s="3" t="n"/>
-    </row>
-    <row r="103">
-      <c r="B103" s="2" t="n">
-        <v>970</v>
-      </c>
-      <c r="C103" s="3" t="inlineStr">
-        <is>
-          <t>신뢰성특성</t>
-        </is>
-      </c>
-      <c r="D103" s="3" t="inlineStr">
-        <is>
-          <t>전기적 특성</t>
-        </is>
-      </c>
-      <c r="E103" s="3" t="inlineStr">
-        <is>
-          <t>3개월 출충(선박심도) 방치 후 용량측정(GB/T)</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="n">
-        <v>94</v>
-      </c>
-      <c r="G103" s="2" t="n"/>
-      <c r="H103" s="2" t="n"/>
-      <c r="I103" s="3" t="inlineStr">
-        <is>
-          <t>≥ 94</t>
-        </is>
-      </c>
-      <c r="J103" s="3" t="n"/>
-      <c r="K103" s="3" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="L103" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M103" s="3" t="inlineStr">
-        <is>
-          <t>선박 수송 조건</t>
-        </is>
-      </c>
-      <c r="N103" s="3" t="inlineStr">
-        <is>
-          <t>GB/T 18287</t>
-        </is>
-      </c>
-      <c r="O103" s="3" t="n"/>
-      <c r="P103" s="3" t="n"/>
-    </row>
-    <row r="104">
-      <c r="B104" s="2" t="n">
-        <v>980</v>
-      </c>
-      <c r="C104" s="3" t="inlineStr">
-        <is>
-          <t>신뢰성특성</t>
-        </is>
-      </c>
-      <c r="D104" s="3" t="inlineStr">
-        <is>
-          <t>전기적 특성</t>
-        </is>
-      </c>
-      <c r="E104" s="3" t="inlineStr">
-        <is>
-          <t>6개월 출충(선박심도)  방치 후 용량측정(GB/T)</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="n">
-        <v>92</v>
-      </c>
-      <c r="G104" s="2" t="n"/>
-      <c r="H104" s="2" t="n"/>
-      <c r="I104" s="3" t="inlineStr">
-        <is>
-          <t>≥ 92</t>
-        </is>
-      </c>
-      <c r="J104" s="3" t="n"/>
-      <c r="K104" s="3" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="L104" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M104" s="3" t="inlineStr">
-        <is>
-          <t>선박 수송 조건</t>
-        </is>
-      </c>
-      <c r="N104" s="3" t="inlineStr">
-        <is>
-          <t>GB/T 18287</t>
-        </is>
-      </c>
-      <c r="O104" s="3" t="n"/>
-      <c r="P104" s="3" t="n"/>
-    </row>
-    <row r="105">
-      <c r="B105" s="2" t="n">
-        <v>990</v>
-      </c>
-      <c r="C105" s="3" t="inlineStr">
-        <is>
-          <t>신뢰성특성</t>
-        </is>
-      </c>
-      <c r="D105" s="3" t="inlineStr">
-        <is>
-          <t>전기적 특성</t>
-        </is>
-      </c>
-      <c r="E105" s="3" t="inlineStr">
-        <is>
-          <t>12개월 출충(선박심도) 방치 후 용량측정(GB/T)</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="G105" s="2" t="n"/>
-      <c r="H105" s="2" t="n"/>
-      <c r="I105" s="3" t="inlineStr">
-        <is>
-          <t>≥ 89</t>
-        </is>
-      </c>
-      <c r="J105" s="3" t="n"/>
-      <c r="K105" s="3" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="L105" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M105" s="3" t="inlineStr">
-        <is>
-          <t>선박 수송 조건</t>
-        </is>
-      </c>
-      <c r="N105" s="3" t="inlineStr">
-        <is>
-          <t>GB/T 18287</t>
-        </is>
-      </c>
-      <c r="O105" s="3" t="n"/>
-      <c r="P105" s="3" t="n"/>
-    </row>
-    <row r="106">
-      <c r="B106" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C106" s="3" t="inlineStr">
-        <is>
-          <t>신뢰성특성</t>
-        </is>
-      </c>
-      <c r="D106" s="3" t="inlineStr">
-        <is>
-          <t>고온방치특성</t>
-        </is>
-      </c>
-      <c r="E106" s="3" t="inlineStr">
-        <is>
-          <t>고온연속충전 두께 3</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="n"/>
-      <c r="G106" s="2" t="n"/>
-      <c r="H106" s="2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="I106" s="3" t="inlineStr">
-        <is>
-          <t>≤ 5.2</t>
-        </is>
-      </c>
-      <c r="J106" s="3" t="n"/>
-      <c r="K106" s="3" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="L106" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="M106" s="3" t="inlineStr">
-        <is>
-          <t>60℃ 7일 연속 충전</t>
-        </is>
-      </c>
-      <c r="N106" s="3" t="inlineStr">
-        <is>
-          <t>MS-EV-401</t>
-        </is>
-      </c>
-      <c r="O106" s="3" t="n"/>
-      <c r="P106" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
